--- a/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC04DF1F-464B-4883-B1AC-4728C438E8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBB5535B-6C0C-48B2-B06F-681C97864A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D51CFD68-D0E8-4639-8672-E80BAD0DAD39}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{77C07481-1624-415F-A3FF-3E1BB9C2EE5A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -135,177 +135,177 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w159527493-220</t>
+  </si>
+  <si>
+    <t>e_w238138373-380</t>
+  </si>
+  <si>
+    <t>e_w260211728-380</t>
+  </si>
+  <si>
+    <t>e_w281804158-220</t>
+  </si>
+  <si>
+    <t>e_w758943072-220</t>
+  </si>
+  <si>
+    <t>e_CH13-220</t>
+  </si>
+  <si>
+    <t>e_CH59-220</t>
+  </si>
+  <si>
+    <t>e_w177392130-400</t>
+  </si>
+  <si>
+    <t>e_w210568055-380</t>
+  </si>
+  <si>
+    <t>e_w281803398-220</t>
+  </si>
+  <si>
+    <t>e_CH42-220</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>e_w109037817-380</t>
+  </si>
+  <si>
+    <t>e_w234983117-220</t>
+  </si>
+  <si>
+    <t>e_w27107779-220</t>
+  </si>
+  <si>
+    <t>e_w100662075-220</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>e_CH45-220</t>
+  </si>
+  <si>
+    <t>e_CH46-220</t>
+  </si>
+  <si>
+    <t>e_CH47-220</t>
+  </si>
+  <si>
+    <t>e_w1092884227-220</t>
+  </si>
+  <si>
+    <t>e_w211907009-220</t>
+  </si>
+  <si>
+    <t>e_w365556107-220</t>
+  </si>
+  <si>
+    <t>e_CH16-380</t>
+  </si>
+  <si>
+    <t>e_CH22-220</t>
+  </si>
+  <si>
+    <t>e_w228003081-220</t>
+  </si>
+  <si>
+    <t>e_w936521586-380</t>
+  </si>
+  <si>
+    <t>e_w1105061707-220</t>
+  </si>
+  <si>
+    <t>e_CH18-220</t>
+  </si>
+  <si>
+    <t>e_CH29-380</t>
+  </si>
+  <si>
+    <t>e_w240959264-220</t>
+  </si>
+  <si>
+    <t>e_w1208713169-220</t>
+  </si>
+  <si>
+    <t>e_CH57-220</t>
+  </si>
+  <si>
+    <t>e_w212498548-220</t>
+  </si>
+  <si>
+    <t>e_w212722603-220</t>
+  </si>
+  <si>
+    <t>e_w36348118-220</t>
+  </si>
+  <si>
+    <t>e_w1086214433-220</t>
+  </si>
+  <si>
+    <t>e_w208780268-380</t>
+  </si>
+  <si>
+    <t>e_w212722603-380</t>
+  </si>
+  <si>
+    <t>e_CH53-225</t>
+  </si>
+  <si>
+    <t>e_w1327084723-220</t>
+  </si>
+  <si>
+    <t>e_w140873735-220</t>
+  </si>
+  <si>
+    <t>e_w969811258-380</t>
+  </si>
+  <si>
+    <t>e_w802058337-220</t>
+  </si>
+  <si>
+    <t>e_w236819191-220</t>
+  </si>
+  <si>
+    <t>e_CH60-225</t>
+  </si>
+  <si>
+    <t>e_CH56-220</t>
+  </si>
+  <si>
+    <t>e_CH17-380</t>
+  </si>
+  <si>
+    <t>e_w431234146-220</t>
+  </si>
+  <si>
+    <t>e_w391576135-220</t>
+  </si>
+  <si>
+    <t>e_w130198336-220</t>
+  </si>
+  <si>
+    <t>e_w55698557-225</t>
+  </si>
+  <si>
+    <t>e_w364949845-380</t>
+  </si>
+  <si>
+    <t>e_CH32-220</t>
+  </si>
+  <si>
+    <t>e_w234983117-380</t>
+  </si>
+  <si>
+    <t>e_w207993342-220</t>
+  </si>
+  <si>
     <t>e_CH27-220</t>
   </si>
   <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
-    <t>e_CH17-380</t>
-  </si>
-  <si>
-    <t>e_CH56-220</t>
-  </si>
-  <si>
-    <t>e_CH60-225</t>
-  </si>
-  <si>
-    <t>e_w236819191-220</t>
-  </si>
-  <si>
-    <t>e_w802058337-220</t>
-  </si>
-  <si>
-    <t>e_w936521586-380</t>
-  </si>
-  <si>
-    <t>e_CH13-220</t>
-  </si>
-  <si>
-    <t>e_CH59-220</t>
-  </si>
-  <si>
-    <t>e_w177392130-400</t>
-  </si>
-  <si>
-    <t>e_w210568055-380</t>
-  </si>
-  <si>
-    <t>e_w281803398-220</t>
-  </si>
-  <si>
-    <t>e_w240959264-220</t>
-  </si>
-  <si>
-    <t>e_w260211728-380</t>
-  </si>
-  <si>
-    <t>e_w281804158-220</t>
-  </si>
-  <si>
-    <t>e_w758943072-220</t>
-  </si>
-  <si>
-    <t>e_CH45-220</t>
-  </si>
-  <si>
-    <t>e_CH46-220</t>
-  </si>
-  <si>
-    <t>e_CH47-220</t>
-  </si>
-  <si>
-    <t>e_w1092884227-220</t>
-  </si>
-  <si>
-    <t>e_w211907009-220</t>
-  </si>
-  <si>
-    <t>e_w391576135-220</t>
-  </si>
-  <si>
-    <t>e_w431234146-220</t>
-  </si>
-  <si>
-    <t>e_w1105061707-220</t>
-  </si>
-  <si>
-    <t>e_w1086214433-220</t>
-  </si>
-  <si>
-    <t>e_w365556107-220</t>
-  </si>
-  <si>
-    <t>e_CH16-380</t>
-  </si>
-  <si>
-    <t>e_CH22-220</t>
-  </si>
-  <si>
-    <t>e_w228003081-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-380</t>
-  </si>
-  <si>
-    <t>e_CH57-220</t>
-  </si>
-  <si>
-    <t>e_w212498548-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-220</t>
-  </si>
-  <si>
-    <t>e_w36348118-220</t>
-  </si>
-  <si>
-    <t>e_CH53-225</t>
-  </si>
-  <si>
-    <t>e_w1327084723-220</t>
-  </si>
-  <si>
-    <t>e_w140873735-220</t>
-  </si>
-  <si>
-    <t>e_w969811258-380</t>
-  </si>
-  <si>
-    <t>e_CH32-220</t>
-  </si>
-  <si>
-    <t>e_w1208713169-220</t>
-  </si>
-  <si>
-    <t>e_w100662075-220</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>e_w55698557-225</t>
-  </si>
-  <si>
-    <t>e_w364949845-380</t>
-  </si>
-  <si>
-    <t>e_w238138373-380</t>
-  </si>
-  <si>
-    <t>e_w234983117-380</t>
-  </si>
-  <si>
-    <t>e_w207993342-220</t>
-  </si>
-  <si>
-    <t>e_w130198336-220</t>
-  </si>
-  <si>
-    <t>e_w27107779-220</t>
-  </si>
-  <si>
-    <t>e_CH18-220</t>
-  </si>
-  <si>
-    <t>e_w159527493-220</t>
-  </si>
-  <si>
-    <t>e_w109037817-380</t>
-  </si>
-  <si>
-    <t>e_w234983117-220</t>
-  </si>
-  <si>
-    <t>e_CH42-220</t>
-  </si>
-  <si>
-    <t>e_CH29-380</t>
-  </si>
-  <si>
-    <t>e_w208780268-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000603509</t>
   </si>
   <si>
@@ -609,6 +609,9 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-CHE_0022</t>
+  </si>
+  <si>
     <t>elc_spv-CHE_0002</t>
   </si>
   <si>
@@ -618,9 +621,6 @@
     <t>elc_spv-CHE_0006</t>
   </si>
   <si>
-    <t>elc_spv-CHE_0022</t>
-  </si>
-  <si>
     <t>ep_solar_pv_000</t>
   </si>
   <si>
@@ -831,15 +831,15 @@
     <t>yes</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Monthey power station_1</t>
   </si>
   <si>
@@ -873,111 +873,165 @@
     <t>Birr power station_GT8</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH27-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/802058337-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/238138373-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/27107779-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/207991759-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/36348118-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/159527493-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/364949845-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/238138373-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/159527493-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/27107779-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/802058337-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - CH46-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1105061707-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1284913429-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/260211728-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1092884227-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH57-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/1086214433-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH57-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/260211728-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH46-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1105061707-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1284913429-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH27-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/55698557-225_Missing Hydro Capacity</t>
   </si>
   <si>
@@ -990,63 +1044,9 @@
     <t>Aggregated Plant - IRENA Gap - CH47-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1092884227-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/365556107-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/207991759-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/36348118-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Amsteg hydroelectric plant_</t>
   </si>
   <si>
@@ -1302,21 +1302,21 @@
     <t>Beznau nuclear power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - CHE_6_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CHE_1_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CHE_2_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - CHE_22_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CHE_2_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CHE_1_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CHE_6_Missing Solar Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant</t>
   </si>
   <si>
@@ -1398,13 +1398,13 @@
     <t>ccs retrofit of -- Cornaux power station_CC1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Birr power station_GT1</t>
@@ -1799,7 +1799,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8545C389-2540-42E2-8A56-C5A479F66086}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A916C175-54CD-461D-9405-91E70CBEB348}">
   <dimension ref="B9:T33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3161,7 +3161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613204A4-C6D2-4DD1-AF2C-22B9A89BAF62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61DB2FF-689D-4727-A7B5-1E8D9CA7A576}">
   <dimension ref="B9:T246"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3985,19 +3985,19 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>8.7169762450973159E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>3162.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I25">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J25">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4038,13 +4038,13 @@
         <v>2022</v>
       </c>
       <c r="F26">
-        <v>7.0487678531784226E-2</v>
+        <v>0.21146303559535268</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3162.5000000000005</v>
+        <v>3162.5</v>
       </c>
       <c r="I26">
         <v>60.500000000000014</v>
@@ -4091,19 +4091,19 @@
         <v>2022</v>
       </c>
       <c r="F27">
-        <v>6.5788499962998598E-2</v>
+        <v>2.6315399985199443E-2</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I27">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J27">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4144,13 +4144,13 @@
         <v>2022</v>
       </c>
       <c r="F28">
-        <v>3.1249537482424337E-2</v>
+        <v>1.9501591060460302E-2</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>3712.5000000000005</v>
+        <v>3712.5</v>
       </c>
       <c r="I28">
         <v>71.5</v>
@@ -4197,19 +4197,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>2.5140605343003043E-2</v>
+        <v>0.1047916820839192</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I29">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J29">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4250,7 +4250,7 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>5.8034855324502345E-2</v>
+        <v>5.9444608895138029E-2</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -4259,7 +4259,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I30">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J30">
         <v>2.3100000000000005</v>
@@ -4303,19 +4303,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>6.0619403537334436E-2</v>
+        <v>2.7960112484274408E-2</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I31">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J31">
-        <v>2.3100000000000005</v>
+        <v>2.5199999999999996</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4356,7 +4356,7 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>3.9943017834677727E-2</v>
+        <v>2.4200769629245916E-2</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -4409,19 +4409,19 @@
         <v>2022</v>
       </c>
       <c r="F33">
-        <v>5.9444608895138029E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I33">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J33">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -4462,19 +4462,19 @@
         <v>2022</v>
       </c>
       <c r="F34">
-        <v>2.7960112484274408E-2</v>
+        <v>0.10925590172426554</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I34">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J34">
-        <v>2.5199999999999996</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -4515,7 +4515,7 @@
         <v>2022</v>
       </c>
       <c r="F35">
-        <v>2.4200769629245916E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4568,19 +4568,19 @@
         <v>2022</v>
       </c>
       <c r="F36">
-        <v>4.2292607119070534E-2</v>
+        <v>7.0487678531784226E-2</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>3712.5000000000009</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I36">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J36">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -4621,19 +4621,19 @@
         <v>2022</v>
       </c>
       <c r="F37">
-        <v>0.10925590172426554</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I37">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J37">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -4668,25 +4668,25 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E38">
         <v>2022</v>
       </c>
       <c r="F38">
-        <v>1.1747946421964037E-2</v>
+        <v>0.38815214978169182</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I38">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J38">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -4721,25 +4721,25 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E39">
         <v>2022</v>
       </c>
       <c r="F39">
-        <v>0.12617294457189376</v>
+        <v>1.1043069636646195E-2</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>3162.5000000000005</v>
+        <v>3712.5</v>
       </c>
       <c r="I39">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J39">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -4774,13 +4774,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E40">
         <v>2022</v>
       </c>
       <c r="F40">
-        <v>2.6315399985199443E-2</v>
+        <v>3.5243839265892113E-2</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4827,19 +4827,19 @@
         <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E41">
         <v>2022</v>
       </c>
       <c r="F41">
-        <v>1.9501591060460302E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>3712.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I41">
         <v>71.5</v>
@@ -4880,25 +4880,25 @@
         <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E42">
         <v>2022</v>
       </c>
       <c r="F42">
-        <v>0.1047916820839192</v>
+        <v>4.3702360689706218E-2</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I42">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J42">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -4933,25 +4933,25 @@
         <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E43">
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>4.3702360689706218E-2</v>
+        <v>7.9886035669355454E-2</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I43">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J43">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K43">
         <v>100</v>
@@ -4986,25 +4986,25 @@
         <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E44">
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>7.9886035669355454E-2</v>
+        <v>2.866498926959225E-2</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I44">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J44">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -5039,25 +5039,25 @@
         <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45">
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>2.866498926959225E-2</v>
+        <v>7.8006364241841208E-2</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I45">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J45">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K45">
         <v>100</v>
@@ -5092,25 +5092,25 @@
         <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>7.8006364241841208E-2</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I46">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J46">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K46">
         <v>100</v>
@@ -5145,13 +5145,13 @@
         <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E47">
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>2.3495892843928074E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -5198,13 +5198,13 @@
         <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>1.4332494634796125E-2</v>
+        <v>1.9031673203581741E-2</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -5251,19 +5251,19 @@
         <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E49">
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>4.2292607119070534E-2</v>
+        <v>4.6521867830977587E-2</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I49">
         <v>71.5</v>
@@ -5304,19 +5304,19 @@
         <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>1.0573151779767634E-2</v>
+        <v>1.7386960704506776E-2</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I50">
         <v>71.5</v>
@@ -5357,25 +5357,25 @@
         <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>9.1164064234440928E-2</v>
+        <v>3.9943017834677727E-2</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I51">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J51">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K51">
         <v>100</v>
@@ -5410,19 +5410,19 @@
         <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>1.1747946421964037E-2</v>
+        <v>1.0573151779767634E-2</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I52">
         <v>71.5</v>
@@ -5463,13 +5463,13 @@
         <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E53">
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>1.9031673203581741E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -5522,19 +5522,19 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>4.6521867830977587E-2</v>
+        <v>0.34844409087545336</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I54">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J54">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K54">
         <v>100</v>
@@ -5575,7 +5575,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>1.7386960704506776E-2</v>
+        <v>1.6447124990749649E-2</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5628,19 +5628,19 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>2.0911344631095986E-2</v>
+        <v>0.12617294457189376</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I56">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J56">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K56">
         <v>100</v>
@@ -5681,19 +5681,19 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>1.268778213572116E-2</v>
+        <v>5.1690964256641762E-2</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I57">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J57">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K57">
         <v>100</v>
@@ -5734,13 +5734,13 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>4.2292607119070534E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I58">
         <v>71.5</v>
@@ -5787,13 +5787,13 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>4.3702360689706218E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I59">
         <v>71.5</v>
@@ -5840,7 +5840,7 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>3.1719455339302899E-2</v>
+        <v>4.3702360689706218E-2</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -5849,7 +5849,7 @@
         <v>3712.5000000000005</v>
       </c>
       <c r="I60">
-        <v>71.499999999999986</v>
+        <v>71.5</v>
       </c>
       <c r="J60">
         <v>2.52</v>
@@ -5893,7 +5893,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>2.1851180344853109E-2</v>
+        <v>3.1719455339302899E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -5902,7 +5902,7 @@
         <v>3712.5000000000005</v>
       </c>
       <c r="I61">
-        <v>71.5</v>
+        <v>71.499999999999986</v>
       </c>
       <c r="J61">
         <v>2.52</v>
@@ -5946,19 +5946,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>2.6785317842078004E-2</v>
+        <v>9.1164064234440928E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I62">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J62">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -5999,7 +5999,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>2.8195071412713692E-2</v>
+        <v>1.5272330348553248E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6011,7 +6011,7 @@
         <v>71.5</v>
       </c>
       <c r="J63">
-        <v>2.5200000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -6052,7 +6052,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>1.7152001776067495E-2</v>
+        <v>2.0911344631095986E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6105,7 +6105,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>2.3965810700806636E-2</v>
+        <v>2.1851180344853109E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6158,19 +6158,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>5.1690964256641762E-2</v>
+        <v>2.6785317842078004E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I66">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J66">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -6211,7 +6211,7 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>3.5243839265892113E-2</v>
+        <v>2.8195071412713692E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6223,7 +6223,7 @@
         <v>71.5</v>
       </c>
       <c r="J67">
-        <v>2.52</v>
+        <v>2.5200000000000005</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6264,7 +6264,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.1747946421964037E-2</v>
+        <v>1.7152001776067495E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6317,7 +6317,7 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.11278028565085477</v>
+        <v>6.0619403537334436E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6370,19 +6370,19 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>1.5037371420113967E-2</v>
+        <v>5.8034855324502345E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I70">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J70">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6423,19 +6423,19 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.21146303559535268</v>
+        <v>2.5140605343003043E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>3162.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I71">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J71">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -6476,7 +6476,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>1.2217864278842598E-2</v>
+        <v>3.1249537482424337E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6529,7 +6529,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>7.8241323170280486E-2</v>
+        <v>6.5788499962998598E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6582,19 +6582,19 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>5.2160882113520331E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>3162.5000000000009</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I74">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J74">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -6635,13 +6635,13 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>1.1043069636646195E-2</v>
+        <v>1.4332494634796125E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>3712.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I75">
         <v>71.5</v>
@@ -6688,19 +6688,19 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.34844409087545336</v>
+        <v>5.2160882113520331E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>2750</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I76">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J76">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -6741,19 +6741,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.268778213572116E-2</v>
+        <v>0.11278028565085477</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I77">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J77">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -6794,7 +6794,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>2.3495892843928074E-2</v>
+        <v>1.5037371420113967E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6847,19 +6847,19 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.38815214978169182</v>
+        <v>2.3965810700806636E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I79">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J79">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -6900,7 +6900,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>1.268778213572116E-2</v>
+        <v>1.2217864278842598E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -6953,19 +6953,19 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>1.6447124990749649E-2</v>
+        <v>7.8241323170280486E-2</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
       <c r="H81">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I81">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J81">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K81">
         <v>100</v>
@@ -7006,19 +7006,19 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>1.5272330348553248E-2</v>
+        <v>8.7169762450973159E-2</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I82">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J82">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K82">
         <v>100</v>
@@ -7053,7 +7053,7 @@
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E83">
         <v>1923</v>
@@ -7106,7 +7106,7 @@
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E84">
         <v>1962</v>
@@ -7212,7 +7212,7 @@
         <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E86">
         <v>1959</v>
@@ -7265,7 +7265,7 @@
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="E87">
         <v>1999</v>
@@ -7318,7 +7318,7 @@
         <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="E88">
         <v>1955</v>
@@ -7477,7 +7477,7 @@
         <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E91">
         <v>1955</v>
@@ -7530,7 +7530,7 @@
         <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E92">
         <v>1957</v>
@@ -7583,7 +7583,7 @@
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>1958</v>
@@ -7636,7 +7636,7 @@
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="E94">
         <v>1965</v>
@@ -7689,7 +7689,7 @@
         <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E95">
         <v>1962</v>
@@ -7742,7 +7742,7 @@
         <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E96">
         <v>1981</v>
@@ -7795,7 +7795,7 @@
         <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="E97">
         <v>1928</v>
@@ -7848,7 +7848,7 @@
         <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="E98">
         <v>2012</v>
@@ -7901,7 +7901,7 @@
         <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="E99">
         <v>1950</v>
@@ -7954,7 +7954,7 @@
         <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E100">
         <v>1967</v>
@@ -8007,7 +8007,7 @@
         <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E101">
         <v>2016</v>
@@ -8060,7 +8060,7 @@
         <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E102">
         <v>1943</v>
@@ -8113,7 +8113,7 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E103">
         <v>1978</v>
@@ -8219,7 +8219,7 @@
         <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E105">
         <v>1910</v>
@@ -8272,7 +8272,7 @@
         <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="E106">
         <v>1960</v>
@@ -8325,7 +8325,7 @@
         <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E107">
         <v>1966</v>
@@ -8378,7 +8378,7 @@
         <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E108">
         <v>1962</v>
@@ -8431,7 +8431,7 @@
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E109">
         <v>1970</v>
@@ -8484,7 +8484,7 @@
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="E110">
         <v>1956</v>
@@ -8537,7 +8537,7 @@
         <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E111">
         <v>1958</v>
@@ -8590,7 +8590,7 @@
         <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E112">
         <v>1957</v>
@@ -8696,7 +8696,7 @@
         <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="E114">
         <v>1968</v>
@@ -8749,7 +8749,7 @@
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E115">
         <v>1961</v>
@@ -8802,7 +8802,7 @@
         <v>31</v>
       </c>
       <c r="D116" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E116">
         <v>2015</v>
@@ -8855,7 +8855,7 @@
         <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E117">
         <v>1965</v>
@@ -8908,7 +8908,7 @@
         <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E118">
         <v>1962</v>
@@ -8961,7 +8961,7 @@
         <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E119">
         <v>1964</v>
@@ -9014,7 +9014,7 @@
         <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E120">
         <v>1953</v>
@@ -9067,7 +9067,7 @@
         <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E121">
         <v>1943</v>
@@ -9120,7 +9120,7 @@
         <v>31</v>
       </c>
       <c r="D122" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E122">
         <v>1928</v>
@@ -9173,7 +9173,7 @@
         <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E123">
         <v>1947</v>
@@ -9226,7 +9226,7 @@
         <v>31</v>
       </c>
       <c r="D124" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="E124">
         <v>1907</v>
@@ -9279,7 +9279,7 @@
         <v>31</v>
       </c>
       <c r="D125" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E125">
         <v>1957</v>
@@ -9332,7 +9332,7 @@
         <v>31</v>
       </c>
       <c r="D126" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E126">
         <v>1992</v>
@@ -9385,7 +9385,7 @@
         <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E127">
         <v>1967</v>
@@ -9438,7 +9438,7 @@
         <v>31</v>
       </c>
       <c r="D128" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E128">
         <v>1926</v>
@@ -9491,7 +9491,7 @@
         <v>31</v>
       </c>
       <c r="D129" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="E129">
         <v>1954</v>
@@ -9544,7 +9544,7 @@
         <v>31</v>
       </c>
       <c r="D130" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="E130">
         <v>1921</v>
@@ -9597,7 +9597,7 @@
         <v>31</v>
       </c>
       <c r="D131" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E131">
         <v>1958</v>
@@ -9650,7 +9650,7 @@
         <v>31</v>
       </c>
       <c r="D132" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E132">
         <v>2014</v>
@@ -9703,7 +9703,7 @@
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E133">
         <v>1937</v>
@@ -9756,7 +9756,7 @@
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E134">
         <v>1962</v>
@@ -9809,7 +9809,7 @@
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E135">
         <v>1923</v>
@@ -9862,7 +9862,7 @@
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E136">
         <v>2016</v>
@@ -9915,7 +9915,7 @@
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="E137">
         <v>1977</v>
@@ -9968,7 +9968,7 @@
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="E138">
         <v>2022</v>
@@ -10021,7 +10021,7 @@
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E139">
         <v>2009</v>
@@ -10074,7 +10074,7 @@
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E140">
         <v>2026</v>
@@ -10180,7 +10180,7 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E142">
         <v>1972</v>
@@ -10233,7 +10233,7 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E143">
         <v>2017</v>
@@ -10286,7 +10286,7 @@
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E144">
         <v>1958</v>
@@ -10339,7 +10339,7 @@
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="E145">
         <v>1976</v>
@@ -10392,7 +10392,7 @@
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E146">
         <v>1955</v>
@@ -10445,7 +10445,7 @@
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E147">
         <v>1926</v>
@@ -10498,7 +10498,7 @@
         <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E148">
         <v>1966</v>
@@ -10551,7 +10551,7 @@
         <v>31</v>
       </c>
       <c r="D149" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E149">
         <v>1950</v>
@@ -10657,7 +10657,7 @@
         <v>31</v>
       </c>
       <c r="D151" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E151">
         <v>1908</v>
@@ -10710,7 +10710,7 @@
         <v>31</v>
       </c>
       <c r="D152" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E152">
         <v>1960</v>
@@ -10763,7 +10763,7 @@
         <v>31</v>
       </c>
       <c r="D153" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E153">
         <v>1925</v>
@@ -10816,7 +10816,7 @@
         <v>31</v>
       </c>
       <c r="D154" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="E154">
         <v>1920</v>
@@ -10869,7 +10869,7 @@
         <v>31</v>
       </c>
       <c r="D155" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E155">
         <v>1975</v>
@@ -10922,7 +10922,7 @@
         <v>31</v>
       </c>
       <c r="D156" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E156">
         <v>1967</v>
@@ -10975,7 +10975,7 @@
         <v>31</v>
       </c>
       <c r="D157" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="E157">
         <v>1952</v>
@@ -11028,7 +11028,7 @@
         <v>31</v>
       </c>
       <c r="D158" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E158">
         <v>1932</v>
@@ -11081,7 +11081,7 @@
         <v>31</v>
       </c>
       <c r="D159" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E159">
         <v>1958</v>
@@ -11134,7 +11134,7 @@
         <v>31</v>
       </c>
       <c r="D160" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E160">
         <v>1920</v>
@@ -11187,7 +11187,7 @@
         <v>31</v>
       </c>
       <c r="D161" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E161">
         <v>1947</v>
@@ -12041,7 +12041,7 @@
         <v>2022</v>
       </c>
       <c r="F177">
-        <v>0.20495809921640443</v>
+        <v>0.21142209564479342</v>
       </c>
       <c r="G177">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         <v>2022</v>
       </c>
       <c r="F178">
-        <v>0.20082137166382633</v>
+        <v>0.20495809921640443</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -12153,7 +12153,7 @@
         <v>2022</v>
       </c>
       <c r="F179">
-        <v>0.2080416632317883</v>
+        <v>0.20082137166382633</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -12209,7 +12209,7 @@
         <v>2022</v>
       </c>
       <c r="F180">
-        <v>0.21142209564479342</v>
+        <v>0.2080416632317883</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -12371,7 +12371,7 @@
         <v>189</v>
       </c>
       <c r="D183" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E183">
         <v>2012</v>
@@ -12427,7 +12427,7 @@
         <v>189</v>
       </c>
       <c r="D184" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E184">
         <v>2015</v>
@@ -13155,7 +13155,7 @@
         <v>189</v>
       </c>
       <c r="D197" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E197">
         <v>2012</v>
@@ -13211,7 +13211,7 @@
         <v>189</v>
       </c>
       <c r="D198" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E198">
         <v>2016</v>
@@ -14814,7 +14814,7 @@
         <v>189</v>
       </c>
       <c r="D236" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E236">
         <v>2012</v>
@@ -15092,7 +15092,7 @@
         <v>240</v>
       </c>
       <c r="D246" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E246">
         <v>2022</v>

--- a/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CD85538-2F3C-4C8E-9E44-C664AC8D547F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D3BE18C-28E4-452D-9013-ED0C33D37D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C87F846D-7E9A-4CD3-B613-7D01327969E0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{29B2B398-0543-4BAB-B53F-013F3E822C3A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -90,15 +90,15 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w1284913429-220</t>
+  </si>
+  <si>
+    <t>e_w161853746-220</t>
+  </si>
+  <si>
     <t>e_w55698557-220</t>
   </si>
   <si>
-    <t>e_w161853746-220</t>
-  </si>
-  <si>
-    <t>e_w1284913429-220</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000410168</t>
   </si>
   <si>
@@ -135,177 +135,177 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w208780268-380</t>
+  </si>
+  <si>
+    <t>e_CH56-220</t>
+  </si>
+  <si>
+    <t>e_CH59-220</t>
+  </si>
+  <si>
+    <t>e_w177392130-400</t>
+  </si>
+  <si>
+    <t>e_w210568055-380</t>
+  </si>
+  <si>
+    <t>e_w281803398-220</t>
+  </si>
+  <si>
+    <t>e_w130198336-220</t>
+  </si>
+  <si>
+    <t>e_w207993342-220</t>
+  </si>
+  <si>
+    <t>e_w234983117-380</t>
+  </si>
+  <si>
+    <t>e_w238138373-380</t>
+  </si>
+  <si>
+    <t>e_w364949845-380</t>
+  </si>
+  <si>
+    <t>e_w55698557-225</t>
+  </si>
+  <si>
+    <t>e_w1086214433-220</t>
+  </si>
+  <si>
+    <t>e_w100662075-220</t>
+  </si>
+  <si>
+    <t>e_w212722603-380</t>
+  </si>
+  <si>
+    <t>e_CH57-220</t>
+  </si>
+  <si>
+    <t>e_w212498548-220</t>
+  </si>
+  <si>
+    <t>e_w212722603-220</t>
+  </si>
+  <si>
+    <t>e_w36348118-220</t>
+  </si>
+  <si>
+    <t>e_CH42-220</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>e_w109037817-380</t>
+  </si>
+  <si>
+    <t>e_w159527493-220</t>
+  </si>
+  <si>
+    <t>e_w27107779-220</t>
+  </si>
+  <si>
+    <t>e_w391576135-220</t>
+  </si>
+  <si>
+    <t>e_w431234146-220</t>
+  </si>
+  <si>
+    <t>e_CH32-220</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>e_w1105061707-220</t>
+  </si>
+  <si>
+    <t>e_w365556107-220</t>
+  </si>
+  <si>
+    <t>e_CH13-220</t>
+  </si>
+  <si>
+    <t>e_w240959264-220</t>
+  </si>
+  <si>
+    <t>e_w260211728-380</t>
+  </si>
+  <si>
+    <t>e_w281804158-220</t>
+  </si>
+  <si>
+    <t>e_w758943072-220</t>
+  </si>
+  <si>
     <t>e_CH16-380</t>
   </si>
   <si>
-    <t>e_w1105061707-220</t>
-  </si>
-  <si>
-    <t>e_w55698557-225</t>
+    <t>e_CH22-220</t>
+  </si>
+  <si>
+    <t>e_w228003081-220</t>
+  </si>
+  <si>
+    <t>e_w234983117-220</t>
+  </si>
+  <si>
+    <t>e_CH53-225</t>
+  </si>
+  <si>
+    <t>e_w1327084723-220</t>
+  </si>
+  <si>
+    <t>e_w140873735-220</t>
+  </si>
+  <si>
+    <t>e_w969811258-380</t>
+  </si>
+  <si>
+    <t>e_w211907009-220</t>
+  </si>
+  <si>
+    <t>e_w1092884227-220</t>
+  </si>
+  <si>
+    <t>e_CH47-220</t>
+  </si>
+  <si>
+    <t>e_CH46-220</t>
+  </si>
+  <si>
+    <t>e_CH45-220</t>
+  </si>
+  <si>
+    <t>e_w936521586-380</t>
+  </si>
+  <si>
+    <t>e_w802058337-220</t>
+  </si>
+  <si>
+    <t>e_CH18-220</t>
+  </si>
+  <si>
+    <t>e_w236819191-220</t>
+  </si>
+  <si>
+    <t>e_CH60-225</t>
   </si>
   <si>
     <t>e_CH27-220</t>
   </si>
   <si>
-    <t>e_w240959264-220</t>
-  </si>
-  <si>
-    <t>e_w260211728-380</t>
-  </si>
-  <si>
-    <t>e_w281804158-220</t>
-  </si>
-  <si>
-    <t>e_w758943072-220</t>
-  </si>
-  <si>
-    <t>e_CH13-220</t>
-  </si>
-  <si>
-    <t>e_CH59-220</t>
-  </si>
-  <si>
-    <t>e_w177392130-400</t>
-  </si>
-  <si>
-    <t>e_w210568055-380</t>
-  </si>
-  <si>
-    <t>e_w281803398-220</t>
+    <t>e_CH17-380</t>
   </si>
   <si>
     <t>e_CH29-380</t>
   </si>
   <si>
-    <t>e_CH22-220</t>
-  </si>
-  <si>
-    <t>e_w228003081-220</t>
-  </si>
-  <si>
-    <t>e_w234983117-220</t>
-  </si>
-  <si>
-    <t>e_w100662075-220</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>e_CH17-380</t>
-  </si>
-  <si>
-    <t>e_CH56-220</t>
-  </si>
-  <si>
-    <t>e_CH60-225</t>
-  </si>
-  <si>
-    <t>e_w236819191-220</t>
-  </si>
-  <si>
-    <t>e_w802058337-220</t>
-  </si>
-  <si>
-    <t>e_w936521586-380</t>
-  </si>
-  <si>
-    <t>e_CH18-220</t>
-  </si>
-  <si>
-    <t>e_w234983117-380</t>
-  </si>
-  <si>
-    <t>e_CH53-225</t>
-  </si>
-  <si>
-    <t>e_w1327084723-220</t>
-  </si>
-  <si>
-    <t>e_w140873735-220</t>
-  </si>
-  <si>
-    <t>e_w969811258-380</t>
-  </si>
-  <si>
-    <t>e_w364949845-380</t>
-  </si>
-  <si>
-    <t>e_CH45-220</t>
-  </si>
-  <si>
-    <t>e_CH46-220</t>
-  </si>
-  <si>
-    <t>e_CH47-220</t>
-  </si>
-  <si>
-    <t>e_w1092884227-220</t>
-  </si>
-  <si>
-    <t>e_w211907009-220</t>
-  </si>
-  <si>
-    <t>e_CH42-220</t>
-  </si>
-  <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
-    <t>e_w109037817-380</t>
-  </si>
-  <si>
-    <t>e_w159527493-220</t>
-  </si>
-  <si>
-    <t>e_w27107779-220</t>
-  </si>
-  <si>
-    <t>e_w391576135-220</t>
-  </si>
-  <si>
-    <t>e_w431234146-220</t>
-  </si>
-  <si>
-    <t>e_w207993342-220</t>
-  </si>
-  <si>
-    <t>e_w130198336-220</t>
-  </si>
-  <si>
     <t>e_w1208713169-220</t>
   </si>
   <si>
-    <t>e_CH32-220</t>
-  </si>
-  <si>
-    <t>e_w36348118-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-220</t>
-  </si>
-  <si>
-    <t>e_w212498548-220</t>
-  </si>
-  <si>
-    <t>e_w1086214433-220</t>
-  </si>
-  <si>
-    <t>e_CH57-220</t>
-  </si>
-  <si>
-    <t>e_w365556107-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-380</t>
-  </si>
-  <si>
-    <t>e_w208780268-380</t>
-  </si>
-  <si>
-    <t>e_w238138373-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000603509</t>
   </si>
   <si>
@@ -834,15 +834,15 @@
     <t>yes</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Monthey power station_1</t>
   </si>
   <si>
@@ -876,180 +876,180 @@
     <t>Birr power station_GT8</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - CH46-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/364949845-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1105061707-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1284913429-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/36348118-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/260211728-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/238138373-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/365556107-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/159527493-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/802058337-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/27107779-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/1086214433-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/207991759-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH27-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - CH57-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/260211728-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/36348118-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/365556107-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/159527493-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/802058337-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - CH56-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH47-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/210568055-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/55698557-225_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/210568055-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH56-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/207991759-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1105061707-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1284913429-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/364949845-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH46-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH27-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/1092884227-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH47-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Amsteg hydroelectric plant_</t>
   </si>
   <si>
@@ -1392,13 +1392,13 @@
     <t>ccs retrofit of -- Cornaux power station_CC1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Birr power station_GT1</t>
@@ -1793,7 +1793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB24A00D-D5A3-4F92-9E97-51409B76D32F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C78D374-3BD4-456A-A9EA-A29E2C84B1E6}">
   <dimension ref="B9:T33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1869,7 +1869,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11">
         <v>0.46865000000000007</v>
@@ -2149,7 +2149,7 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E16">
         <v>0.27938750000000001</v>
@@ -2205,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E17">
         <v>0.27938750000000001</v>
@@ -2261,7 +2261,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>0.27938750000000001</v>
@@ -2317,7 +2317,7 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <v>0.27938750000000001</v>
@@ -2373,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>0.27938750000000001</v>
@@ -2429,7 +2429,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21">
         <v>0.27938750000000001</v>
@@ -2485,7 +2485,7 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>0.27938750000000001</v>
@@ -2541,7 +2541,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>0.27938750000000001</v>
@@ -2597,7 +2597,7 @@
         <v>178</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>0.450625</v>
@@ -2709,7 +2709,7 @@
         <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26">
         <v>0.27037500000000003</v>
@@ -2765,7 +2765,7 @@
         <v>178</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E27">
         <v>0.27037500000000003</v>
@@ -2821,7 +2821,7 @@
         <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E28">
         <v>0.27037500000000003</v>
@@ -2877,7 +2877,7 @@
         <v>178</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E29">
         <v>0.27037500000000003</v>
@@ -2933,7 +2933,7 @@
         <v>178</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E30">
         <v>0.27037500000000003</v>
@@ -2989,7 +2989,7 @@
         <v>178</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E31">
         <v>0.27037500000000003</v>
@@ -3045,7 +3045,7 @@
         <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>0.27037500000000003</v>
@@ -3101,7 +3101,7 @@
         <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E33">
         <v>0.27037500000000003</v>
@@ -3155,7 +3155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626C3D15-96A7-4DD4-9A22-822EE8B1CE0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2E96AE-4A91-43D2-8518-5C67759A8C5B}">
   <dimension ref="B9:T246"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3290,19 +3290,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>2.0664375715922109E-2</v>
+        <v>9.4079266895761751E-2</v>
       </c>
       <c r="G12">
-        <v>0.57680000000000009</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H12">
-        <v>1485.0000000000002</v>
+        <v>1265</v>
       </c>
       <c r="I12">
-        <v>42.900000000000006</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J12">
-        <v>3.7800000000000002</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -3396,19 +3396,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>9.4079266895761751E-2</v>
+        <v>2.0664375715922109E-2</v>
       </c>
       <c r="G14">
-        <v>0.59739999999999993</v>
+        <v>0.57680000000000009</v>
       </c>
       <c r="H14">
-        <v>1265</v>
+        <v>1485.0000000000002</v>
       </c>
       <c r="I14">
-        <v>36.300000000000004</v>
+        <v>42.900000000000006</v>
       </c>
       <c r="J14">
-        <v>3.4650000000000003</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -3443,7 +3443,7 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>2009</v>
@@ -3549,7 +3549,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E17">
         <v>2023</v>
@@ -3602,7 +3602,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>2023</v>
@@ -3655,7 +3655,7 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <v>2023</v>
@@ -3708,7 +3708,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>2023</v>
@@ -3761,7 +3761,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21">
         <v>2023</v>
@@ -3814,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>2023</v>
@@ -3867,7 +3867,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>2023</v>
@@ -3920,7 +3920,7 @@
         <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>2023</v>
@@ -3979,7 +3979,7 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>1.9031673203581741E-2</v>
+        <v>1.5272330348553248E-2</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -4032,13 +4032,13 @@
         <v>2022</v>
       </c>
       <c r="F26">
-        <v>1.0573151779767634E-2</v>
+        <v>3.1249537482424337E-2</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I26">
         <v>71.5</v>
@@ -4085,19 +4085,19 @@
         <v>2022</v>
       </c>
       <c r="F27">
-        <v>0.11278028565085477</v>
+        <v>2.7960112484274408E-2</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I27">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J27">
-        <v>2.3100000000000005</v>
+        <v>2.5199999999999996</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4138,19 +4138,19 @@
         <v>2022</v>
       </c>
       <c r="F28">
-        <v>8.7169762450973159E-2</v>
+        <v>2.4200769629245916E-2</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>3162.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I28">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J28">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4191,19 +4191,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.12617294457189376</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I29">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J29">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4244,19 +4244,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>2.6315399985199443E-2</v>
+        <v>0.10925590172426554</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I30">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J30">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -4297,19 +4297,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>1.9501591060460302E-2</v>
+        <v>5.2160882113520331E-2</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>3712.5</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I31">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J31">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4350,7 +4350,7 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.1047916820839192</v>
+        <v>7.8241323170280486E-2</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -4403,19 +4403,19 @@
         <v>2022</v>
       </c>
       <c r="F33">
-        <v>5.9444608895138029E-2</v>
+        <v>1.2217864278842598E-2</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I33">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J33">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -4456,19 +4456,19 @@
         <v>2022</v>
       </c>
       <c r="F34">
-        <v>2.7960112484274408E-2</v>
+        <v>0.21146303559535268</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>3712.5000000000005</v>
+        <v>3162.5</v>
       </c>
       <c r="I34">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J34">
-        <v>2.5199999999999996</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -4509,7 +4509,7 @@
         <v>2022</v>
       </c>
       <c r="F35">
-        <v>2.4200769629245916E-2</v>
+        <v>1.5037371420113967E-2</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4562,19 +4562,19 @@
         <v>2022</v>
       </c>
       <c r="F36">
-        <v>4.2292607119070534E-2</v>
+        <v>0.11278028565085477</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>3712.5000000000009</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I36">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J36">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -4615,7 +4615,7 @@
         <v>2022</v>
       </c>
       <c r="F37">
-        <v>0.10925590172426554</v>
+        <v>9.1164064234440928E-2</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4624,7 +4624,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I37">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J37">
         <v>2.3100000000000005</v>
@@ -4668,7 +4668,7 @@
         <v>2022</v>
       </c>
       <c r="F38">
-        <v>1.6447124990749649E-2</v>
+        <v>3.5243839265892113E-2</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>2022</v>
       </c>
       <c r="F39">
-        <v>4.6521867830977587E-2</v>
+        <v>2.0911344631095986E-2</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4774,7 +4774,7 @@
         <v>2022</v>
       </c>
       <c r="F40">
-        <v>1.7386960704506776E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4827,19 +4827,19 @@
         <v>2022</v>
       </c>
       <c r="F41">
-        <v>0.38815214978169182</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>2750</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I41">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J41">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K41">
         <v>100</v>
@@ -4880,7 +4880,7 @@
         <v>2022</v>
       </c>
       <c r="F42">
-        <v>3.5243839265892113E-2</v>
+        <v>4.3702360689706218E-2</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -4933,7 +4933,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>1.1747946421964037E-2</v>
+        <v>3.1719455339302899E-2</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4942,7 +4942,7 @@
         <v>3712.5000000000005</v>
       </c>
       <c r="I43">
-        <v>71.5</v>
+        <v>71.499999999999986</v>
       </c>
       <c r="J43">
         <v>2.52</v>
@@ -4986,19 +4986,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>6.5788499962998598E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I44">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J44">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -5039,19 +5039,19 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>3.1249537482424337E-2</v>
+        <v>7.0487678531784226E-2</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I45">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J45">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K45">
         <v>100</v>
@@ -5092,7 +5092,7 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>2.5140605343003043E-2</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -5145,19 +5145,19 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>5.8034855324502345E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I47">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J47">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K47">
         <v>100</v>
@@ -5198,19 +5198,19 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>6.0619403537334436E-2</v>
+        <v>1.1043069636646195E-2</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48">
-        <v>3162.5000000000005</v>
+        <v>3712.5</v>
       </c>
       <c r="I48">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J48">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K48">
         <v>100</v>
@@ -5251,7 +5251,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>3.9943017834677727E-2</v>
+        <v>1.4332494634796125E-2</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -5304,19 +5304,19 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.34844409087545336</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50">
-        <v>2750</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I50">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J50">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K50">
         <v>100</v>
@@ -5357,7 +5357,7 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>1.2217864278842598E-2</v>
+        <v>2.3965810700806636E-2</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5410,7 +5410,7 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>2.1851180344853109E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5463,13 +5463,13 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>2.6785317842078004E-2</v>
+        <v>1.0573151779767634E-2</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I53">
         <v>71.5</v>
@@ -5510,13 +5510,13 @@
         <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="E54">
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>2.8195071412713692E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5528,7 +5528,7 @@
         <v>71.5</v>
       </c>
       <c r="J54">
-        <v>2.5200000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K54">
         <v>100</v>
@@ -5563,13 +5563,13 @@
         <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>1.7152001776067495E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5616,25 +5616,25 @@
         <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>1.5037371420113967E-2</v>
+        <v>5.9444608895138029E-2</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I56">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J56">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K56">
         <v>100</v>
@@ -5669,25 +5669,25 @@
         <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>4.3702360689706218E-2</v>
+        <v>0.12617294457189376</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I57">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J57">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K57">
         <v>100</v>
@@ -5722,25 +5722,25 @@
         <v>31</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>7.9886035669355454E-2</v>
+        <v>2.6315399985199443E-2</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I58">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J58">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K58">
         <v>100</v>
@@ -5775,19 +5775,19 @@
         <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>2.866498926959225E-2</v>
+        <v>1.9501591060460302E-2</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59">
-        <v>3712.5000000000005</v>
+        <v>3712.5</v>
       </c>
       <c r="I59">
         <v>71.5</v>
@@ -5828,13 +5828,13 @@
         <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>7.8006364241841208E-2</v>
+        <v>0.1047916820839192</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -5881,13 +5881,13 @@
         <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>2.3495892843928074E-2</v>
+        <v>1.9031673203581741E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -5934,13 +5934,13 @@
         <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.268778213572116E-2</v>
+        <v>4.6521867830977587E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5987,25 +5987,25 @@
         <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>7.0487678531784226E-2</v>
+        <v>1.7386960704506776E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I63">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J63">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -6040,25 +6040,25 @@
         <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>2.3495892843928074E-2</v>
+        <v>0.38815214978169182</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I64">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J64">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -6093,13 +6093,13 @@
         <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>1.268778213572116E-2</v>
+        <v>2.1851180344853109E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6146,19 +6146,19 @@
         <v>31</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>1.1043069636646195E-2</v>
+        <v>2.6785317842078004E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3712.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I66">
         <v>71.5</v>
@@ -6199,13 +6199,13 @@
         <v>31</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>1.4332494634796125E-2</v>
+        <v>2.8195071412713692E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6217,7 +6217,7 @@
         <v>71.5</v>
       </c>
       <c r="J67">
-        <v>2.52</v>
+        <v>2.5200000000000005</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6252,19 +6252,19 @@
         <v>31</v>
       </c>
       <c r="D68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>4.2292607119070534E-2</v>
+        <v>1.7152001776067495E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I68">
         <v>71.5</v>
@@ -6305,25 +6305,25 @@
         <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>7.8241323170280486E-2</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I69">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J69">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6358,19 +6358,19 @@
         <v>31</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>5.2160882113520331E-2</v>
+        <v>7.8006364241841208E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>3162.5000000000009</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I70">
         <v>60.500000000000014</v>
@@ -6411,25 +6411,25 @@
         <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>5.1690964256641762E-2</v>
+        <v>2.866498926959225E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I71">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J71">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -6464,25 +6464,25 @@
         <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>2.3965810700806636E-2</v>
+        <v>7.9886035669355454E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I72">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J72">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -6517,13 +6517,13 @@
         <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>3.1719455339302899E-2</v>
+        <v>4.3702360689706218E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6532,7 +6532,7 @@
         <v>3712.5000000000005</v>
       </c>
       <c r="I73">
-        <v>71.499999999999986</v>
+        <v>71.5</v>
       </c>
       <c r="J73">
         <v>2.52</v>
@@ -6570,13 +6570,13 @@
         <v>31</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>4.3702360689706218E-2</v>
+        <v>3.9943017834677727E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -6623,25 +6623,25 @@
         <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E75">
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>4.2292607119070534E-2</v>
+        <v>6.0619403537334436E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>3712.5000000000009</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I75">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J75">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K75">
         <v>100</v>
@@ -6676,25 +6676,25 @@
         <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>9.1164064234440928E-2</v>
+        <v>0.34844409087545336</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I76">
-        <v>60.500000000000021</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J76">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -6729,25 +6729,25 @@
         <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>1.268778213572116E-2</v>
+        <v>5.8034855324502345E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I77">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J77">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -6782,13 +6782,13 @@
         <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="E78">
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>1.1747946421964037E-2</v>
+        <v>2.5140605343003043E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6841,19 +6841,19 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>1.1747946421964037E-2</v>
+        <v>8.7169762450973159E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I79">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J79">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -6894,19 +6894,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>2.0911344631095986E-2</v>
+        <v>6.5788499962998598E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I80">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J80">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -6947,7 +6947,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>1.5272330348553248E-2</v>
+        <v>1.6447124990749649E-2</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -7000,13 +7000,13 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.21146303559535268</v>
+        <v>5.1690964256641762E-2</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>3162.5</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I82">
         <v>60.500000000000014</v>
@@ -7047,7 +7047,7 @@
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E83">
         <v>1923</v>
@@ -7100,7 +7100,7 @@
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E84">
         <v>1962</v>
@@ -7153,7 +7153,7 @@
         <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E85">
         <v>1966</v>
@@ -7206,7 +7206,7 @@
         <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E86">
         <v>1959</v>
@@ -7259,7 +7259,7 @@
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="E87">
         <v>1999</v>
@@ -7312,7 +7312,7 @@
         <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E88">
         <v>1955</v>
@@ -7365,7 +7365,7 @@
         <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E89">
         <v>1969</v>
@@ -7418,7 +7418,7 @@
         <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E90">
         <v>1959</v>
@@ -7471,7 +7471,7 @@
         <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E91">
         <v>1955</v>
@@ -7524,7 +7524,7 @@
         <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="E92">
         <v>1957</v>
@@ -7577,7 +7577,7 @@
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="E93">
         <v>1958</v>
@@ -7630,7 +7630,7 @@
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E94">
         <v>1965</v>
@@ -7683,7 +7683,7 @@
         <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="E95">
         <v>1962</v>
@@ -7736,7 +7736,7 @@
         <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="E96">
         <v>1981</v>
@@ -7789,7 +7789,7 @@
         <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E97">
         <v>1928</v>
@@ -7842,7 +7842,7 @@
         <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E98">
         <v>2012</v>
@@ -7895,7 +7895,7 @@
         <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E99">
         <v>1950</v>
@@ -7948,7 +7948,7 @@
         <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E100">
         <v>1967</v>
@@ -8001,7 +8001,7 @@
         <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E101">
         <v>2016</v>
@@ -8054,7 +8054,7 @@
         <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E102">
         <v>1943</v>
@@ -8107,7 +8107,7 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E103">
         <v>1978</v>
@@ -8160,7 +8160,7 @@
         <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E104">
         <v>1976</v>
@@ -8213,7 +8213,7 @@
         <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E105">
         <v>1910</v>
@@ -8266,7 +8266,7 @@
         <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="E106">
         <v>1960</v>
@@ -8319,7 +8319,7 @@
         <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E107">
         <v>1966</v>
@@ -8372,7 +8372,7 @@
         <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>1962</v>
@@ -8425,7 +8425,7 @@
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E109">
         <v>1970</v>
@@ -8478,7 +8478,7 @@
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E110">
         <v>1956</v>
@@ -8531,7 +8531,7 @@
         <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E111">
         <v>1958</v>
@@ -8584,7 +8584,7 @@
         <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="E112">
         <v>1957</v>
@@ -8637,7 +8637,7 @@
         <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E113">
         <v>1978</v>
@@ -8690,7 +8690,7 @@
         <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E114">
         <v>1968</v>
@@ -8743,7 +8743,7 @@
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="E115">
         <v>1961</v>
@@ -8796,7 +8796,7 @@
         <v>31</v>
       </c>
       <c r="D116" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="E116">
         <v>2015</v>
@@ -8849,7 +8849,7 @@
         <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E117">
         <v>1965</v>
@@ -8902,7 +8902,7 @@
         <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E118">
         <v>1962</v>
@@ -8955,7 +8955,7 @@
         <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E119">
         <v>1964</v>
@@ -9008,7 +9008,7 @@
         <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E120">
         <v>1953</v>
@@ -9061,7 +9061,7 @@
         <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E121">
         <v>1943</v>
@@ -9114,7 +9114,7 @@
         <v>31</v>
       </c>
       <c r="D122" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E122">
         <v>1928</v>
@@ -9167,7 +9167,7 @@
         <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E123">
         <v>1947</v>
@@ -9220,7 +9220,7 @@
         <v>31</v>
       </c>
       <c r="D124" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E124">
         <v>1907</v>
@@ -9273,7 +9273,7 @@
         <v>31</v>
       </c>
       <c r="D125" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E125">
         <v>1957</v>
@@ -9326,7 +9326,7 @@
         <v>31</v>
       </c>
       <c r="D126" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E126">
         <v>1992</v>
@@ -9379,7 +9379,7 @@
         <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E127">
         <v>1967</v>
@@ -9432,7 +9432,7 @@
         <v>31</v>
       </c>
       <c r="D128" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E128">
         <v>1926</v>
@@ -9485,7 +9485,7 @@
         <v>31</v>
       </c>
       <c r="D129" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="E129">
         <v>1954</v>
@@ -9538,7 +9538,7 @@
         <v>31</v>
       </c>
       <c r="D130" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E130">
         <v>1921</v>
@@ -9591,7 +9591,7 @@
         <v>31</v>
       </c>
       <c r="D131" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E131">
         <v>1958</v>
@@ -9644,7 +9644,7 @@
         <v>31</v>
       </c>
       <c r="D132" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E132">
         <v>2014</v>
@@ -9697,7 +9697,7 @@
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E133">
         <v>1937</v>
@@ -9750,7 +9750,7 @@
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E134">
         <v>1962</v>
@@ -9803,7 +9803,7 @@
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="E135">
         <v>1923</v>
@@ -9856,7 +9856,7 @@
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E136">
         <v>2016</v>
@@ -9909,7 +9909,7 @@
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E137">
         <v>1977</v>
@@ -9962,7 +9962,7 @@
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="E138">
         <v>2022</v>
@@ -10015,7 +10015,7 @@
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E139">
         <v>2009</v>
@@ -10068,7 +10068,7 @@
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E140">
         <v>2026</v>
@@ -10121,7 +10121,7 @@
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E141">
         <v>1968</v>
@@ -10174,7 +10174,7 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E142">
         <v>1972</v>
@@ -10227,7 +10227,7 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E143">
         <v>2017</v>
@@ -10280,7 +10280,7 @@
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="E144">
         <v>1958</v>
@@ -10333,7 +10333,7 @@
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E145">
         <v>1976</v>
@@ -10386,7 +10386,7 @@
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E146">
         <v>1955</v>
@@ -10439,7 +10439,7 @@
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E147">
         <v>1926</v>
@@ -10492,7 +10492,7 @@
         <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E148">
         <v>1966</v>
@@ -10545,7 +10545,7 @@
         <v>31</v>
       </c>
       <c r="D149" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E149">
         <v>1950</v>
@@ -10598,7 +10598,7 @@
         <v>31</v>
       </c>
       <c r="D150" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E150">
         <v>1959</v>
@@ -10651,7 +10651,7 @@
         <v>31</v>
       </c>
       <c r="D151" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E151">
         <v>1908</v>
@@ -10704,7 +10704,7 @@
         <v>31</v>
       </c>
       <c r="D152" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E152">
         <v>1960</v>
@@ -10757,7 +10757,7 @@
         <v>31</v>
       </c>
       <c r="D153" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E153">
         <v>1925</v>
@@ -10810,7 +10810,7 @@
         <v>31</v>
       </c>
       <c r="D154" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E154">
         <v>1920</v>
@@ -10863,7 +10863,7 @@
         <v>31</v>
       </c>
       <c r="D155" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="E155">
         <v>1975</v>
@@ -10916,7 +10916,7 @@
         <v>31</v>
       </c>
       <c r="D156" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="E156">
         <v>1967</v>
@@ -10969,7 +10969,7 @@
         <v>31</v>
       </c>
       <c r="D157" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E157">
         <v>1952</v>
@@ -11022,7 +11022,7 @@
         <v>31</v>
       </c>
       <c r="D158" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E158">
         <v>1932</v>
@@ -11075,7 +11075,7 @@
         <v>31</v>
       </c>
       <c r="D159" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E159">
         <v>1958</v>
@@ -11128,7 +11128,7 @@
         <v>31</v>
       </c>
       <c r="D160" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="E160">
         <v>1920</v>
@@ -11181,7 +11181,7 @@
         <v>31</v>
       </c>
       <c r="D161" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="E161">
         <v>1947</v>
@@ -11234,7 +11234,7 @@
         <v>31</v>
       </c>
       <c r="D162" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E162">
         <v>1952</v>
@@ -11499,7 +11499,7 @@
         <v>178</v>
       </c>
       <c r="D167" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E167">
         <v>2009</v>
@@ -11605,7 +11605,7 @@
         <v>178</v>
       </c>
       <c r="D169" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E169">
         <v>2023</v>
@@ -11658,7 +11658,7 @@
         <v>178</v>
       </c>
       <c r="D170" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E170">
         <v>2023</v>
@@ -11711,7 +11711,7 @@
         <v>178</v>
       </c>
       <c r="D171" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E171">
         <v>2023</v>
@@ -11764,7 +11764,7 @@
         <v>178</v>
       </c>
       <c r="D172" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E172">
         <v>2023</v>
@@ -11817,7 +11817,7 @@
         <v>178</v>
       </c>
       <c r="D173" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E173">
         <v>2023</v>
@@ -11870,7 +11870,7 @@
         <v>178</v>
       </c>
       <c r="D174" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E174">
         <v>2023</v>
@@ -11923,7 +11923,7 @@
         <v>178</v>
       </c>
       <c r="D175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E175">
         <v>2023</v>
@@ -11976,7 +11976,7 @@
         <v>178</v>
       </c>
       <c r="D176" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E176">
         <v>2023</v>
@@ -12147,7 +12147,7 @@
         <v>2022</v>
       </c>
       <c r="F179">
-        <v>0.18842349602545536</v>
+        <v>0.18842349602545541</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -14072,7 +14072,7 @@
         <v>2022</v>
       </c>
       <c r="F216">
-        <v>0.17802636513312506</v>
+        <v>0.17802636513312517</v>
       </c>
       <c r="G216">
         <v>1</v>
@@ -14807,7 +14807,7 @@
         <v>2022</v>
       </c>
       <c r="F237">
-        <v>0.1548167752144102</v>
+        <v>0.15481677521441034</v>
       </c>
       <c r="G237">
         <v>1</v>
@@ -15044,7 +15044,7 @@
         <v>241</v>
       </c>
       <c r="D246" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E246">
         <v>2022</v>

--- a/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D3BE18C-28E4-452D-9013-ED0C33D37D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16F6E6D5-E0C7-446D-A815-69B2FB687394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{29B2B398-0543-4BAB-B53F-013F3E822C3A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CB5DED2D-868B-4E76-AD55-6CEC7D7A69EF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -90,15 +90,15 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w55698557-220</t>
+  </si>
+  <si>
     <t>e_w1284913429-220</t>
   </si>
   <si>
     <t>e_w161853746-220</t>
   </si>
   <si>
-    <t>e_w55698557-220</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000410168</t>
   </si>
   <si>
@@ -135,177 +135,177 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w281804158-220</t>
+  </si>
+  <si>
+    <t>e_w236819191-220</t>
+  </si>
+  <si>
+    <t>e_w391576135-220</t>
+  </si>
+  <si>
+    <t>e_w431234146-220</t>
+  </si>
+  <si>
+    <t>e_CH53-225</t>
+  </si>
+  <si>
+    <t>e_w1327084723-220</t>
+  </si>
+  <si>
+    <t>e_w140873735-220</t>
+  </si>
+  <si>
+    <t>e_w969811258-380</t>
+  </si>
+  <si>
+    <t>e_CH18-220</t>
+  </si>
+  <si>
+    <t>e_CH29-380</t>
+  </si>
+  <si>
+    <t>e_CH27-220</t>
+  </si>
+  <si>
+    <t>e_w240959264-220</t>
+  </si>
+  <si>
+    <t>e_w260211728-380</t>
+  </si>
+  <si>
+    <t>e_CH46-220</t>
+  </si>
+  <si>
+    <t>e_w758943072-220</t>
+  </si>
+  <si>
+    <t>e_CH57-220</t>
+  </si>
+  <si>
+    <t>e_w212498548-220</t>
+  </si>
+  <si>
+    <t>e_w212722603-220</t>
+  </si>
+  <si>
+    <t>e_w36348118-220</t>
+  </si>
+  <si>
+    <t>e_w130198336-220</t>
+  </si>
+  <si>
+    <t>e_w207993342-220</t>
+  </si>
+  <si>
+    <t>e_w234983117-380</t>
+  </si>
+  <si>
+    <t>e_w238138373-380</t>
+  </si>
+  <si>
+    <t>e_w364949845-380</t>
+  </si>
+  <si>
+    <t>e_w55698557-225</t>
+  </si>
+  <si>
+    <t>e_CH45-220</t>
+  </si>
+  <si>
+    <t>e_w109037817-380</t>
+  </si>
+  <si>
+    <t>e_CH47-220</t>
+  </si>
+  <si>
+    <t>e_w1092884227-220</t>
+  </si>
+  <si>
+    <t>e_w211907009-220</t>
+  </si>
+  <si>
+    <t>e_CH16-380</t>
+  </si>
+  <si>
+    <t>e_w27107779-220</t>
+  </si>
+  <si>
+    <t>e_w228003081-220</t>
+  </si>
+  <si>
+    <t>e_w234983117-220</t>
+  </si>
+  <si>
+    <t>e_w100662075-220</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>e_w1105061707-220</t>
+  </si>
+  <si>
+    <t>e_CH13-220</t>
+  </si>
+  <si>
+    <t>e_CH59-220</t>
+  </si>
+  <si>
+    <t>e_w177392130-400</t>
+  </si>
+  <si>
+    <t>e_w210568055-380</t>
+  </si>
+  <si>
+    <t>e_w281803398-220</t>
+  </si>
+  <si>
+    <t>e_w365556107-220</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>e_CH42-220</t>
+  </si>
+  <si>
+    <t>e_w212722603-380</t>
+  </si>
+  <si>
     <t>e_w208780268-380</t>
   </si>
   <si>
+    <t>e_w1086214433-220</t>
+  </si>
+  <si>
+    <t>e_w1208713169-220</t>
+  </si>
+  <si>
+    <t>e_CH32-220</t>
+  </si>
+  <si>
+    <t>e_CH17-380</t>
+  </si>
+  <si>
+    <t>e_w936521586-380</t>
+  </si>
+  <si>
+    <t>e_w802058337-220</t>
+  </si>
+  <si>
+    <t>e_CH22-220</t>
+  </si>
+  <si>
+    <t>e_CH60-225</t>
+  </si>
+  <si>
     <t>e_CH56-220</t>
   </si>
   <si>
-    <t>e_CH59-220</t>
-  </si>
-  <si>
-    <t>e_w177392130-400</t>
-  </si>
-  <si>
-    <t>e_w210568055-380</t>
-  </si>
-  <si>
-    <t>e_w281803398-220</t>
-  </si>
-  <si>
-    <t>e_w130198336-220</t>
-  </si>
-  <si>
-    <t>e_w207993342-220</t>
-  </si>
-  <si>
-    <t>e_w234983117-380</t>
-  </si>
-  <si>
-    <t>e_w238138373-380</t>
-  </si>
-  <si>
-    <t>e_w364949845-380</t>
-  </si>
-  <si>
-    <t>e_w55698557-225</t>
-  </si>
-  <si>
-    <t>e_w1086214433-220</t>
-  </si>
-  <si>
-    <t>e_w100662075-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-380</t>
-  </si>
-  <si>
-    <t>e_CH57-220</t>
-  </si>
-  <si>
-    <t>e_w212498548-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-220</t>
-  </si>
-  <si>
-    <t>e_w36348118-220</t>
-  </si>
-  <si>
-    <t>e_CH42-220</t>
-  </si>
-  <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
-    <t>e_w109037817-380</t>
-  </si>
-  <si>
     <t>e_w159527493-220</t>
   </si>
   <si>
-    <t>e_w27107779-220</t>
-  </si>
-  <si>
-    <t>e_w391576135-220</t>
-  </si>
-  <si>
-    <t>e_w431234146-220</t>
-  </si>
-  <si>
-    <t>e_CH32-220</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>e_w1105061707-220</t>
-  </si>
-  <si>
-    <t>e_w365556107-220</t>
-  </si>
-  <si>
-    <t>e_CH13-220</t>
-  </si>
-  <si>
-    <t>e_w240959264-220</t>
-  </si>
-  <si>
-    <t>e_w260211728-380</t>
-  </si>
-  <si>
-    <t>e_w281804158-220</t>
-  </si>
-  <si>
-    <t>e_w758943072-220</t>
-  </si>
-  <si>
-    <t>e_CH16-380</t>
-  </si>
-  <si>
-    <t>e_CH22-220</t>
-  </si>
-  <si>
-    <t>e_w228003081-220</t>
-  </si>
-  <si>
-    <t>e_w234983117-220</t>
-  </si>
-  <si>
-    <t>e_CH53-225</t>
-  </si>
-  <si>
-    <t>e_w1327084723-220</t>
-  </si>
-  <si>
-    <t>e_w140873735-220</t>
-  </si>
-  <si>
-    <t>e_w969811258-380</t>
-  </si>
-  <si>
-    <t>e_w211907009-220</t>
-  </si>
-  <si>
-    <t>e_w1092884227-220</t>
-  </si>
-  <si>
-    <t>e_CH47-220</t>
-  </si>
-  <si>
-    <t>e_CH46-220</t>
-  </si>
-  <si>
-    <t>e_CH45-220</t>
-  </si>
-  <si>
-    <t>e_w936521586-380</t>
-  </si>
-  <si>
-    <t>e_w802058337-220</t>
-  </si>
-  <si>
-    <t>e_CH18-220</t>
-  </si>
-  <si>
-    <t>e_w236819191-220</t>
-  </si>
-  <si>
-    <t>e_CH60-225</t>
-  </si>
-  <si>
-    <t>e_CH27-220</t>
-  </si>
-  <si>
-    <t>e_CH17-380</t>
-  </si>
-  <si>
-    <t>e_CH29-380</t>
-  </si>
-  <si>
-    <t>e_w1208713169-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000603509</t>
   </si>
   <si>
@@ -837,12 +837,12 @@
     <t>Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Monthey power station_1</t>
   </si>
   <si>
@@ -876,180 +876,180 @@
     <t>Birr power station_GT8</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/802058337-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/159527493-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/27107779-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/238138373-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/365556107-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1092884227-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1086214433-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH57-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/36348118-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH56-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/55698557-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH47-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/210568055-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH27-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/364949845-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - CH46-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/364949845-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/1105061707-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/1284913429-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/36348118-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/260211728-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/238138373-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/365556107-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/159527493-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/802058337-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/27107779-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1086214433-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/207991759-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH27-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH57-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH56-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH47-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/210568055-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/55698557-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1092884227-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Amsteg hydroelectric plant_</t>
   </si>
   <si>
@@ -1392,10 +1392,10 @@
     <t>ccs retrofit of -- Cornaux power station_CC1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
@@ -1793,7 +1793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C78D374-3BD4-456A-A9EA-A29E2C84B1E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37704F02-2DAD-400B-8CC8-1224956A0804}">
   <dimension ref="B9:T33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1869,7 +1869,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>0.46865000000000007</v>
@@ -1925,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>0.36951250000000002</v>
@@ -2149,7 +2149,7 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>0.27938750000000001</v>
@@ -2205,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>0.27938750000000001</v>
@@ -2261,7 +2261,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>0.27938750000000001</v>
@@ -2317,7 +2317,7 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>0.27938750000000001</v>
@@ -2373,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>0.27938750000000001</v>
@@ -2429,7 +2429,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>0.27938750000000001</v>
@@ -2485,7 +2485,7 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>0.27938750000000001</v>
@@ -2541,7 +2541,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>0.27938750000000001</v>
@@ -2597,7 +2597,7 @@
         <v>178</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>0.450625</v>
@@ -2653,7 +2653,7 @@
         <v>178</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>0.35148750000000001</v>
@@ -2709,7 +2709,7 @@
         <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E26">
         <v>0.27037500000000003</v>
@@ -2765,7 +2765,7 @@
         <v>178</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E27">
         <v>0.27037500000000003</v>
@@ -2821,7 +2821,7 @@
         <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28">
         <v>0.27037500000000003</v>
@@ -2877,7 +2877,7 @@
         <v>178</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29">
         <v>0.27037500000000003</v>
@@ -2933,7 +2933,7 @@
         <v>178</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E30">
         <v>0.27037500000000003</v>
@@ -2989,7 +2989,7 @@
         <v>178</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>0.27037500000000003</v>
@@ -3045,7 +3045,7 @@
         <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E32">
         <v>0.27037500000000003</v>
@@ -3101,7 +3101,7 @@
         <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <v>0.27037500000000003</v>
@@ -3155,7 +3155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2E96AE-4A91-43D2-8518-5C67759A8C5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02320C4A-D1D4-4132-A48C-6BFDEAE214E3}">
   <dimension ref="B9:T246"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3290,19 +3290,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>9.4079266895761751E-2</v>
+        <v>2.0664375715922109E-2</v>
       </c>
       <c r="G12">
-        <v>0.59739999999999993</v>
+        <v>0.57680000000000009</v>
       </c>
       <c r="H12">
-        <v>1265</v>
+        <v>1485.0000000000002</v>
       </c>
       <c r="I12">
-        <v>36.300000000000004</v>
+        <v>42.900000000000006</v>
       </c>
       <c r="J12">
-        <v>3.4650000000000003</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -3343,19 +3343,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>1.6456357388316155E-2</v>
+        <v>9.4079266895761751E-2</v>
       </c>
       <c r="G13">
-        <v>0.57680000000000009</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H13">
-        <v>1485.0000000000002</v>
+        <v>1265</v>
       </c>
       <c r="I13">
-        <v>42.900000000000006</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J13">
-        <v>3.78</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -3396,7 +3396,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>2.0664375715922109E-2</v>
+        <v>1.6456357388316155E-2</v>
       </c>
       <c r="G14">
         <v>0.57680000000000009</v>
@@ -3408,7 +3408,7 @@
         <v>42.900000000000006</v>
       </c>
       <c r="J14">
-        <v>3.7800000000000002</v>
+        <v>3.78</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -3443,7 +3443,7 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <v>2009</v>
@@ -3496,7 +3496,7 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16">
         <v>1988</v>
@@ -3549,7 +3549,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>2023</v>
@@ -3602,7 +3602,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>2023</v>
@@ -3655,7 +3655,7 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>2023</v>
@@ -3708,7 +3708,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>2023</v>
@@ -3761,7 +3761,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>2023</v>
@@ -3814,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>2023</v>
@@ -3867,7 +3867,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>2023</v>
@@ -3920,7 +3920,7 @@
         <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>2023</v>
@@ -3979,13 +3979,13 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>1.5272330348553248E-2</v>
+        <v>1.9501591060460302E-2</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>3712.5000000000005</v>
+        <v>3712.5</v>
       </c>
       <c r="I25">
         <v>71.5</v>
@@ -4032,19 +4032,19 @@
         <v>2022</v>
       </c>
       <c r="F26">
-        <v>3.1249537482424337E-2</v>
+        <v>5.8034855324502345E-2</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I26">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J26">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4085,7 +4085,7 @@
         <v>2022</v>
       </c>
       <c r="F27">
-        <v>2.7960112484274408E-2</v>
+        <v>1.4332494634796125E-2</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -4097,7 +4097,7 @@
         <v>71.5</v>
       </c>
       <c r="J27">
-        <v>2.5199999999999996</v>
+        <v>2.52</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4138,13 +4138,13 @@
         <v>2022</v>
       </c>
       <c r="F28">
-        <v>2.4200769629245916E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I28">
         <v>71.5</v>
@@ -4191,13 +4191,13 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>4.2292607119070534E-2</v>
+        <v>2.1851180344853109E-2</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I29">
         <v>71.5</v>
@@ -4244,19 +4244,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.10925590172426554</v>
+        <v>2.6785317842078004E-2</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I30">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J30">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -4297,19 +4297,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>5.2160882113520331E-2</v>
+        <v>2.8195071412713692E-2</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>3162.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I31">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J31">
-        <v>2.3100000000000005</v>
+        <v>2.5200000000000005</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4350,19 +4350,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>7.8241323170280486E-2</v>
+        <v>1.7152001776067495E-2</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I32">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J32">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -4403,19 +4403,19 @@
         <v>2022</v>
       </c>
       <c r="F33">
-        <v>1.2217864278842598E-2</v>
+        <v>0.34844409087545336</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I33">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J33">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -4456,19 +4456,19 @@
         <v>2022</v>
       </c>
       <c r="F34">
-        <v>0.21146303559535268</v>
+        <v>1.6447124990749649E-2</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>3162.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I34">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J34">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -4509,19 +4509,19 @@
         <v>2022</v>
       </c>
       <c r="F35">
-        <v>1.5037371420113967E-2</v>
+        <v>8.7169762450973159E-2</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I35">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J35">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -4562,7 +4562,7 @@
         <v>2022</v>
       </c>
       <c r="F36">
-        <v>0.11278028565085477</v>
+        <v>0.12617294457189376</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -4615,19 +4615,19 @@
         <v>2022</v>
       </c>
       <c r="F37">
-        <v>9.1164064234440928E-2</v>
+        <v>2.6315399985199443E-2</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I37">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J37">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -4668,19 +4668,19 @@
         <v>2022</v>
       </c>
       <c r="F38">
-        <v>3.5243839265892113E-2</v>
+        <v>7.9886035669355454E-2</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I38">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J38">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -4721,19 +4721,19 @@
         <v>2022</v>
       </c>
       <c r="F39">
-        <v>2.0911344631095986E-2</v>
+        <v>0.1047916820839192</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I39">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J39">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -4986,19 +4986,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>1.268778213572116E-2</v>
+        <v>5.2160882113520331E-2</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I44">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J44">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -5039,7 +5039,7 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>7.0487678531784226E-2</v>
+        <v>7.8241323170280486E-2</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -5092,7 +5092,7 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>2.3495892843928074E-2</v>
+        <v>1.2217864278842598E-2</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -5145,19 +5145,19 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>1.268778213572116E-2</v>
+        <v>0.21146303559535268</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47">
-        <v>3712.5000000000005</v>
+        <v>3162.5</v>
       </c>
       <c r="I47">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J47">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K47">
         <v>100</v>
@@ -5198,13 +5198,13 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>1.1043069636646195E-2</v>
+        <v>1.5037371420113967E-2</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48">
-        <v>3712.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I48">
         <v>71.5</v>
@@ -5251,19 +5251,19 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>1.4332494634796125E-2</v>
+        <v>0.11278028565085477</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I49">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J49">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K49">
         <v>100</v>
@@ -5304,13 +5304,13 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>4.2292607119070534E-2</v>
+        <v>4.3702360689706218E-2</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I50">
         <v>71.5</v>
@@ -5357,7 +5357,7 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>2.3965810700806636E-2</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5410,7 +5410,7 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>1.1747946421964037E-2</v>
+        <v>2.866498926959225E-2</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5463,19 +5463,19 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>1.0573151779767634E-2</v>
+        <v>7.8006364241841208E-2</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53">
-        <v>3712.5000000000009</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I53">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J53">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K53">
         <v>100</v>
@@ -5510,13 +5510,13 @@
         <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="E54">
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>1.1747946421964037E-2</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5563,13 +5563,13 @@
         <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>1.1747946421964037E-2</v>
+        <v>1.9031673203581741E-2</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5616,25 +5616,25 @@
         <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>5.9444608895138029E-2</v>
+        <v>1.1043069636646195E-2</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>3162.5000000000005</v>
+        <v>3712.5</v>
       </c>
       <c r="I56">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J56">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K56">
         <v>100</v>
@@ -5669,25 +5669,25 @@
         <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.12617294457189376</v>
+        <v>1.7386960704506776E-2</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I57">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J57">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K57">
         <v>100</v>
@@ -5722,25 +5722,25 @@
         <v>31</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>2.6315399985199443E-2</v>
+        <v>0.38815214978169182</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I58">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J58">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K58">
         <v>100</v>
@@ -5775,19 +5775,19 @@
         <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>1.9501591060460302E-2</v>
+        <v>3.5243839265892113E-2</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59">
-        <v>3712.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I59">
         <v>71.5</v>
@@ -5828,25 +5828,25 @@
         <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.1047916820839192</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I60">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J60">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K60">
         <v>100</v>
@@ -5881,19 +5881,19 @@
         <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>1.9031673203581741E-2</v>
+        <v>1.0573151779767634E-2</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I61">
         <v>71.5</v>
@@ -5934,13 +5934,13 @@
         <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>4.6521867830977587E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5993,19 +5993,19 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>1.7386960704506776E-2</v>
+        <v>5.9444608895138029E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I63">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J63">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -6046,19 +6046,19 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.38815214978169182</v>
+        <v>2.7960112484274408E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I64">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J64">
-        <v>2.1</v>
+        <v>2.5199999999999996</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -6099,7 +6099,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>2.1851180344853109E-2</v>
+        <v>2.4200769629245916E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6152,13 +6152,13 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>2.6785317842078004E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I66">
         <v>71.5</v>
@@ -6205,19 +6205,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>2.8195071412713692E-2</v>
+        <v>0.10925590172426554</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I67">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J67">
-        <v>2.5200000000000005</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6258,7 +6258,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>1.7152001776067495E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6311,19 +6311,19 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>2.3495892843928074E-2</v>
+        <v>7.0487678531784226E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I69">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J69">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6364,19 +6364,19 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>7.8006364241841208E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I70">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J70">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6417,7 +6417,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>2.866498926959225E-2</v>
+        <v>2.0911344631095986E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6470,19 +6470,19 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>7.9886035669355454E-2</v>
+        <v>1.5272330348553248E-2</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I72">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J72">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -6523,19 +6523,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>4.3702360689706218E-2</v>
+        <v>9.1164064234440928E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I73">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J73">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -6576,19 +6576,19 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>3.9943017834677727E-2</v>
+        <v>5.1690964256641762E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I74">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J74">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -6629,19 +6629,19 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>6.0619403537334436E-2</v>
+        <v>2.3965810700806636E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I75">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J75">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K75">
         <v>100</v>
@@ -6682,19 +6682,19 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.34844409087545336</v>
+        <v>6.5788499962998598E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I76">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J76">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -6735,19 +6735,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>5.8034855324502345E-2</v>
+        <v>3.9943017834677727E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I77">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J77">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -6788,19 +6788,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>2.5140605343003043E-2</v>
+        <v>6.0619403537334436E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I78">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J78">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K78">
         <v>100</v>
@@ -6841,19 +6841,19 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>8.7169762450973159E-2</v>
+        <v>4.6521867830977587E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>3162.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I79">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J79">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -6894,19 +6894,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>6.5788499962998598E-2</v>
+        <v>2.5140605343003043E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I80">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J80">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -6947,7 +6947,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>1.6447124990749649E-2</v>
+        <v>3.1249537482424337E-2</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -7000,19 +7000,19 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>5.1690964256641762E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I82">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J82">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K82">
         <v>100</v>
@@ -7047,7 +7047,7 @@
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="E83">
         <v>1923</v>
@@ -7100,7 +7100,7 @@
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E84">
         <v>1962</v>
@@ -7153,7 +7153,7 @@
         <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E85">
         <v>1966</v>
@@ -7206,7 +7206,7 @@
         <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="E86">
         <v>1959</v>
@@ -7259,7 +7259,7 @@
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E87">
         <v>1999</v>
@@ -7312,7 +7312,7 @@
         <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E88">
         <v>1955</v>
@@ -7365,7 +7365,7 @@
         <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E89">
         <v>1969</v>
@@ -7418,7 +7418,7 @@
         <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="E90">
         <v>1959</v>
@@ -7471,7 +7471,7 @@
         <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="E91">
         <v>1955</v>
@@ -7524,7 +7524,7 @@
         <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E92">
         <v>1957</v>
@@ -7577,7 +7577,7 @@
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E93">
         <v>1958</v>
@@ -7630,7 +7630,7 @@
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="E94">
         <v>1965</v>
@@ -7683,7 +7683,7 @@
         <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E95">
         <v>1962</v>
@@ -7736,7 +7736,7 @@
         <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="E96">
         <v>1981</v>
@@ -7789,7 +7789,7 @@
         <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E97">
         <v>1928</v>
@@ -7842,7 +7842,7 @@
         <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E98">
         <v>2012</v>
@@ -7895,7 +7895,7 @@
         <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E99">
         <v>1950</v>
@@ -7948,7 +7948,7 @@
         <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E100">
         <v>1967</v>
@@ -8001,7 +8001,7 @@
         <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E101">
         <v>2016</v>
@@ -8054,7 +8054,7 @@
         <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E102">
         <v>1943</v>
@@ -8107,7 +8107,7 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E103">
         <v>1978</v>
@@ -8160,7 +8160,7 @@
         <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E104">
         <v>1976</v>
@@ -8213,7 +8213,7 @@
         <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E105">
         <v>1910</v>
@@ -8266,7 +8266,7 @@
         <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E106">
         <v>1960</v>
@@ -8319,7 +8319,7 @@
         <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="E107">
         <v>1966</v>
@@ -8372,7 +8372,7 @@
         <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E108">
         <v>1962</v>
@@ -8425,7 +8425,7 @@
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E109">
         <v>1970</v>
@@ -8478,7 +8478,7 @@
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E110">
         <v>1956</v>
@@ -8584,7 +8584,7 @@
         <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E112">
         <v>1957</v>
@@ -8637,7 +8637,7 @@
         <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E113">
         <v>1978</v>
@@ -8690,7 +8690,7 @@
         <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="E114">
         <v>1968</v>
@@ -8743,7 +8743,7 @@
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E115">
         <v>1961</v>
@@ -8796,7 +8796,7 @@
         <v>31</v>
       </c>
       <c r="D116" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E116">
         <v>2015</v>
@@ -8849,7 +8849,7 @@
         <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="E117">
         <v>1965</v>
@@ -8902,7 +8902,7 @@
         <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E118">
         <v>1962</v>
@@ -8955,7 +8955,7 @@
         <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E119">
         <v>1964</v>
@@ -9008,7 +9008,7 @@
         <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="E120">
         <v>1953</v>
@@ -9061,7 +9061,7 @@
         <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="E121">
         <v>1943</v>
@@ -9114,7 +9114,7 @@
         <v>31</v>
       </c>
       <c r="D122" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E122">
         <v>1928</v>
@@ -9167,7 +9167,7 @@
         <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E123">
         <v>1947</v>
@@ -9220,7 +9220,7 @@
         <v>31</v>
       </c>
       <c r="D124" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E124">
         <v>1907</v>
@@ -9326,7 +9326,7 @@
         <v>31</v>
       </c>
       <c r="D126" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E126">
         <v>1992</v>
@@ -9379,7 +9379,7 @@
         <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E127">
         <v>1967</v>
@@ -9432,7 +9432,7 @@
         <v>31</v>
       </c>
       <c r="D128" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E128">
         <v>1926</v>
@@ -9485,7 +9485,7 @@
         <v>31</v>
       </c>
       <c r="D129" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="E129">
         <v>1954</v>
@@ -9538,7 +9538,7 @@
         <v>31</v>
       </c>
       <c r="D130" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E130">
         <v>1921</v>
@@ -9697,7 +9697,7 @@
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E133">
         <v>1937</v>
@@ -9803,7 +9803,7 @@
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E135">
         <v>1923</v>
@@ -9856,7 +9856,7 @@
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E136">
         <v>2016</v>
@@ -9909,7 +9909,7 @@
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E137">
         <v>1977</v>
@@ -9962,7 +9962,7 @@
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E138">
         <v>2022</v>
@@ -10015,7 +10015,7 @@
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E139">
         <v>2009</v>
@@ -10068,7 +10068,7 @@
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E140">
         <v>2026</v>
@@ -10121,7 +10121,7 @@
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E141">
         <v>1968</v>
@@ -10174,7 +10174,7 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E142">
         <v>1972</v>
@@ -10227,7 +10227,7 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E143">
         <v>2017</v>
@@ -10280,7 +10280,7 @@
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="E144">
         <v>1958</v>
@@ -10333,7 +10333,7 @@
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E145">
         <v>1976</v>
@@ -10386,7 +10386,7 @@
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E146">
         <v>1955</v>
@@ -10439,7 +10439,7 @@
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E147">
         <v>1926</v>
@@ -10492,7 +10492,7 @@
         <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E148">
         <v>1966</v>
@@ -10545,7 +10545,7 @@
         <v>31</v>
       </c>
       <c r="D149" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="E149">
         <v>1950</v>
@@ -10598,7 +10598,7 @@
         <v>31</v>
       </c>
       <c r="D150" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="E150">
         <v>1959</v>
@@ -10651,7 +10651,7 @@
         <v>31</v>
       </c>
       <c r="D151" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E151">
         <v>1908</v>
@@ -10704,7 +10704,7 @@
         <v>31</v>
       </c>
       <c r="D152" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E152">
         <v>1960</v>
@@ -10810,7 +10810,7 @@
         <v>31</v>
       </c>
       <c r="D154" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E154">
         <v>1920</v>
@@ -10863,7 +10863,7 @@
         <v>31</v>
       </c>
       <c r="D155" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E155">
         <v>1975</v>
@@ -10916,7 +10916,7 @@
         <v>31</v>
       </c>
       <c r="D156" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E156">
         <v>1967</v>
@@ -10969,7 +10969,7 @@
         <v>31</v>
       </c>
       <c r="D157" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="E157">
         <v>1952</v>
@@ -11022,7 +11022,7 @@
         <v>31</v>
       </c>
       <c r="D158" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="E158">
         <v>1932</v>
@@ -11075,7 +11075,7 @@
         <v>31</v>
       </c>
       <c r="D159" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="E159">
         <v>1958</v>
@@ -11128,7 +11128,7 @@
         <v>31</v>
       </c>
       <c r="D160" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E160">
         <v>1920</v>
@@ -11181,7 +11181,7 @@
         <v>31</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E161">
         <v>1947</v>
@@ -11234,7 +11234,7 @@
         <v>31</v>
       </c>
       <c r="D162" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E162">
         <v>1952</v>
@@ -11499,7 +11499,7 @@
         <v>178</v>
       </c>
       <c r="D167" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E167">
         <v>2009</v>
@@ -11552,7 +11552,7 @@
         <v>178</v>
       </c>
       <c r="D168" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E168">
         <v>1988</v>
@@ -11605,7 +11605,7 @@
         <v>178</v>
       </c>
       <c r="D169" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E169">
         <v>2023</v>
@@ -11658,7 +11658,7 @@
         <v>178</v>
       </c>
       <c r="D170" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E170">
         <v>2023</v>
@@ -11711,7 +11711,7 @@
         <v>178</v>
       </c>
       <c r="D171" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E171">
         <v>2023</v>
@@ -11764,7 +11764,7 @@
         <v>178</v>
       </c>
       <c r="D172" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E172">
         <v>2023</v>
@@ -11817,7 +11817,7 @@
         <v>178</v>
       </c>
       <c r="D173" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E173">
         <v>2023</v>
@@ -11870,7 +11870,7 @@
         <v>178</v>
       </c>
       <c r="D174" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E174">
         <v>2023</v>
@@ -11923,7 +11923,7 @@
         <v>178</v>
       </c>
       <c r="D175" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E175">
         <v>2023</v>
@@ -11976,7 +11976,7 @@
         <v>178</v>
       </c>
       <c r="D176" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E176">
         <v>2023</v>
@@ -12053,7 +12053,7 @@
         <v>33</v>
       </c>
       <c r="L177">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N177" t="s">
         <v>259</v>
@@ -12165,7 +12165,7 @@
         <v>33</v>
       </c>
       <c r="L179">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N179" t="s">
         <v>259</v>
@@ -12333,7 +12333,7 @@
         <v>33</v>
       </c>
       <c r="L182">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N182" t="s">
         <v>259</v>
@@ -12389,7 +12389,7 @@
         <v>33</v>
       </c>
       <c r="L183">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N183" t="s">
         <v>259</v>
@@ -12669,7 +12669,7 @@
         <v>33</v>
       </c>
       <c r="L188">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N188" t="s">
         <v>259</v>
@@ -12949,7 +12949,7 @@
         <v>33</v>
       </c>
       <c r="L193">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N193" t="s">
         <v>259</v>
@@ -13061,7 +13061,7 @@
         <v>33</v>
       </c>
       <c r="L195">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N195" t="s">
         <v>259</v>
@@ -13229,7 +13229,7 @@
         <v>33</v>
       </c>
       <c r="L198">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N198" t="s">
         <v>259</v>
@@ -13341,7 +13341,7 @@
         <v>33</v>
       </c>
       <c r="L200">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N200" t="s">
         <v>259</v>
@@ -13397,7 +13397,7 @@
         <v>33</v>
       </c>
       <c r="L201">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N201" t="s">
         <v>259</v>
@@ -13621,7 +13621,7 @@
         <v>33</v>
       </c>
       <c r="L205">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
       <c r="N205" t="s">
         <v>259</v>
@@ -13845,7 +13845,7 @@
         <v>33</v>
       </c>
       <c r="L209">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="210" spans="2:12" x14ac:dyDescent="0.45">
@@ -13880,7 +13880,7 @@
         <v>33</v>
       </c>
       <c r="L210">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="211" spans="2:12" x14ac:dyDescent="0.45">
@@ -13915,7 +13915,7 @@
         <v>33</v>
       </c>
       <c r="L211">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="212" spans="2:12" x14ac:dyDescent="0.45">
@@ -14090,7 +14090,7 @@
         <v>33</v>
       </c>
       <c r="L216">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.45">
@@ -14265,7 +14265,7 @@
         <v>33</v>
       </c>
       <c r="L221">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="222" spans="2:12" x14ac:dyDescent="0.45">
@@ -14335,7 +14335,7 @@
         <v>33</v>
       </c>
       <c r="L223">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="224" spans="2:12" x14ac:dyDescent="0.45">
@@ -14370,7 +14370,7 @@
         <v>33</v>
       </c>
       <c r="L224">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="225" spans="2:12" x14ac:dyDescent="0.45">
@@ -14580,7 +14580,7 @@
         <v>33</v>
       </c>
       <c r="L230">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="231" spans="2:12" x14ac:dyDescent="0.45">
@@ -14615,7 +14615,7 @@
         <v>33</v>
       </c>
       <c r="L231">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="232" spans="2:12" x14ac:dyDescent="0.45">
@@ -14650,7 +14650,7 @@
         <v>33</v>
       </c>
       <c r="L232">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="233" spans="2:12" x14ac:dyDescent="0.45">
@@ -14755,7 +14755,7 @@
         <v>33</v>
       </c>
       <c r="L235">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="236" spans="2:12" x14ac:dyDescent="0.45">
@@ -14825,7 +14825,7 @@
         <v>33</v>
       </c>
       <c r="L237">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="238" spans="2:12" x14ac:dyDescent="0.45">
@@ -14860,7 +14860,7 @@
         <v>33</v>
       </c>
       <c r="L238">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="239" spans="2:12" x14ac:dyDescent="0.45">
@@ -14895,7 +14895,7 @@
         <v>33</v>
       </c>
       <c r="L239">
-        <v>0.16885857771052631</v>
+        <v>0.16885857771052634</v>
       </c>
     </row>
     <row r="240" spans="2:12" x14ac:dyDescent="0.45">
@@ -15044,7 +15044,7 @@
         <v>241</v>
       </c>
       <c r="D246" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E246">
         <v>2022</v>

--- a/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE_grids/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16F6E6D5-E0C7-446D-A815-69B2FB687394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14CFB998-4082-4A24-902E-3BFE2A6FB34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CB5DED2D-868B-4E76-AD55-6CEC7D7A69EF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{92D55390-7046-4DE9-ABDB-F58426FE4F47}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -93,12 +93,12 @@
     <t>e_w55698557-220</t>
   </si>
   <si>
+    <t>e_w161853746-220</t>
+  </si>
+  <si>
     <t>e_w1284913429-220</t>
   </si>
   <si>
-    <t>e_w161853746-220</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000410168</t>
   </si>
   <si>
@@ -135,177 +135,177 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w236819191-220</t>
+  </si>
+  <si>
+    <t>e_w208780268-380</t>
+  </si>
+  <si>
+    <t>e_CH18-220</t>
+  </si>
+  <si>
+    <t>e_CH29-380</t>
+  </si>
+  <si>
+    <t>e_CH27-220</t>
+  </si>
+  <si>
+    <t>e_w240959264-220</t>
+  </si>
+  <si>
+    <t>e_w260211728-380</t>
+  </si>
+  <si>
     <t>e_w281804158-220</t>
   </si>
   <si>
-    <t>e_w236819191-220</t>
+    <t>e_w758943072-220</t>
+  </si>
+  <si>
+    <t>e_w365556107-220</t>
+  </si>
+  <si>
+    <t>e_CH17-380</t>
+  </si>
+  <si>
+    <t>e_CH56-220</t>
+  </si>
+  <si>
+    <t>e_CH60-225</t>
+  </si>
+  <si>
+    <t>e_CH47-220</t>
+  </si>
+  <si>
+    <t>e_w802058337-220</t>
+  </si>
+  <si>
+    <t>e_w936521586-380</t>
+  </si>
+  <si>
+    <t>e_w130198336-220</t>
+  </si>
+  <si>
+    <t>e_w207993342-220</t>
+  </si>
+  <si>
+    <t>e_w234983117-380</t>
+  </si>
+  <si>
+    <t>e_w238138373-380</t>
+  </si>
+  <si>
+    <t>e_w364949845-380</t>
+  </si>
+  <si>
+    <t>e_w55698557-225</t>
+  </si>
+  <si>
+    <t>e_w1105061707-220</t>
+  </si>
+  <si>
+    <t>e_CH45-220</t>
+  </si>
+  <si>
+    <t>e_CH46-220</t>
+  </si>
+  <si>
+    <t>e_w1327084723-220</t>
+  </si>
+  <si>
+    <t>e_w1092884227-220</t>
+  </si>
+  <si>
+    <t>e_w211907009-220</t>
+  </si>
+  <si>
+    <t>e_CH57-220</t>
+  </si>
+  <si>
+    <t>e_w212498548-220</t>
+  </si>
+  <si>
+    <t>e_w969811258-380</t>
+  </si>
+  <si>
+    <t>e_w36348118-220</t>
+  </si>
+  <si>
+    <t>e_CH16-380</t>
+  </si>
+  <si>
+    <t>e_CH22-220</t>
+  </si>
+  <si>
+    <t>e_w228003081-220</t>
+  </si>
+  <si>
+    <t>e_w234983117-220</t>
+  </si>
+  <si>
+    <t>e_CH42-220</t>
+  </si>
+  <si>
+    <t>e_r7933294-380</t>
+  </si>
+  <si>
+    <t>e_w109037817-380</t>
+  </si>
+  <si>
+    <t>e_w159527493-220</t>
+  </si>
+  <si>
+    <t>e_w27107779-220</t>
+  </si>
+  <si>
+    <t>e_w100662075-220</t>
+  </si>
+  <si>
+    <t>e_w207991759-380</t>
+  </si>
+  <si>
+    <t>e_CH53-225</t>
+  </si>
+  <si>
+    <t>e_w1208713169-220</t>
+  </si>
+  <si>
+    <t>e_CH32-220</t>
+  </si>
+  <si>
+    <t>e_w281803398-220</t>
+  </si>
+  <si>
+    <t>e_w210568055-380</t>
+  </si>
+  <si>
+    <t>e_w177392130-400</t>
+  </si>
+  <si>
+    <t>e_CH59-220</t>
   </si>
   <si>
     <t>e_w391576135-220</t>
   </si>
   <si>
+    <t>e_CH13-220</t>
+  </si>
+  <si>
+    <t>e_w212722603-380</t>
+  </si>
+  <si>
+    <t>e_w212722603-220</t>
+  </si>
+  <si>
+    <t>e_w1086214433-220</t>
+  </si>
+  <si>
     <t>e_w431234146-220</t>
   </si>
   <si>
-    <t>e_CH53-225</t>
-  </si>
-  <si>
-    <t>e_w1327084723-220</t>
-  </si>
-  <si>
     <t>e_w140873735-220</t>
   </si>
   <si>
-    <t>e_w969811258-380</t>
-  </si>
-  <si>
-    <t>e_CH18-220</t>
-  </si>
-  <si>
-    <t>e_CH29-380</t>
-  </si>
-  <si>
-    <t>e_CH27-220</t>
-  </si>
-  <si>
-    <t>e_w240959264-220</t>
-  </si>
-  <si>
-    <t>e_w260211728-380</t>
-  </si>
-  <si>
-    <t>e_CH46-220</t>
-  </si>
-  <si>
-    <t>e_w758943072-220</t>
-  </si>
-  <si>
-    <t>e_CH57-220</t>
-  </si>
-  <si>
-    <t>e_w212498548-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-220</t>
-  </si>
-  <si>
-    <t>e_w36348118-220</t>
-  </si>
-  <si>
-    <t>e_w130198336-220</t>
-  </si>
-  <si>
-    <t>e_w207993342-220</t>
-  </si>
-  <si>
-    <t>e_w234983117-380</t>
-  </si>
-  <si>
-    <t>e_w238138373-380</t>
-  </si>
-  <si>
-    <t>e_w364949845-380</t>
-  </si>
-  <si>
-    <t>e_w55698557-225</t>
-  </si>
-  <si>
-    <t>e_CH45-220</t>
-  </si>
-  <si>
-    <t>e_w109037817-380</t>
-  </si>
-  <si>
-    <t>e_CH47-220</t>
-  </si>
-  <si>
-    <t>e_w1092884227-220</t>
-  </si>
-  <si>
-    <t>e_w211907009-220</t>
-  </si>
-  <si>
-    <t>e_CH16-380</t>
-  </si>
-  <si>
-    <t>e_w27107779-220</t>
-  </si>
-  <si>
-    <t>e_w228003081-220</t>
-  </si>
-  <si>
-    <t>e_w234983117-220</t>
-  </si>
-  <si>
-    <t>e_w100662075-220</t>
-  </si>
-  <si>
-    <t>e_w207991759-380</t>
-  </si>
-  <si>
-    <t>e_w1105061707-220</t>
-  </si>
-  <si>
-    <t>e_CH13-220</t>
-  </si>
-  <si>
-    <t>e_CH59-220</t>
-  </si>
-  <si>
-    <t>e_w177392130-400</t>
-  </si>
-  <si>
-    <t>e_w210568055-380</t>
-  </si>
-  <si>
-    <t>e_w281803398-220</t>
-  </si>
-  <si>
-    <t>e_w365556107-220</t>
-  </si>
-  <si>
-    <t>e_r7933294-380</t>
-  </si>
-  <si>
-    <t>e_CH42-220</t>
-  </si>
-  <si>
-    <t>e_w212722603-380</t>
-  </si>
-  <si>
-    <t>e_w208780268-380</t>
-  </si>
-  <si>
-    <t>e_w1086214433-220</t>
-  </si>
-  <si>
-    <t>e_w1208713169-220</t>
-  </si>
-  <si>
-    <t>e_CH32-220</t>
-  </si>
-  <si>
-    <t>e_CH17-380</t>
-  </si>
-  <si>
-    <t>e_w936521586-380</t>
-  </si>
-  <si>
-    <t>e_w802058337-220</t>
-  </si>
-  <si>
-    <t>e_CH22-220</t>
-  </si>
-  <si>
-    <t>e_CH60-225</t>
-  </si>
-  <si>
-    <t>e_CH56-220</t>
-  </si>
-  <si>
-    <t>e_w159527493-220</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000603509</t>
   </si>
   <si>
@@ -834,15 +834,15 @@
     <t>yes</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Monthey power station_1</t>
   </si>
   <si>
@@ -876,180 +876,180 @@
     <t>Birr power station_GT8</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/1086214433-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH57-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/365556107-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1092884227-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/27107779-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/238138373-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/802058337-220_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/210568055-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH56-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/55698557-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH47-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH46-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/207991759-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/260211728-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/159527493-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CH13-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/27107779-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/238138373-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - relation/7933294-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH59-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/365556107-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1092884227-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH32-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1086214433-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH57-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH45-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH42-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/758943072-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212498548-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH60-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/236819191-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH16-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/100662075-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/177392130-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/936521586-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/364949845-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1105061707-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1284913429-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/36348118-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CH18-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/211907009-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/281803398-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH56-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/55698557-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH47-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/210568055-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH17-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1208713169-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/208780268-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/281804158-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/130198336-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH29-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/212722603-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/207993342-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH22-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - CH27-220_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CH53-225_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1327084723-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/391576135-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/140873735-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/364949845-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CH46-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/228003081-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/234983117-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1105061707-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109037817-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/431234146-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/969811258-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/240959264-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1284913429-220_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/260211728-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/207991759-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Amsteg hydroelectric plant_</t>
   </si>
   <si>
@@ -1392,10 +1392,10 @@
     <t>ccs retrofit of -- Cornaux power station_CC1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1284913429-220_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/161853746-220_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/55698557-220_Missing Gas Capacity</t>
@@ -1793,7 +1793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37704F02-2DAD-400B-8CC8-1224956A0804}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BDE17F-261F-46E5-8273-7CCD2FECFA58}">
   <dimension ref="B9:T33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1925,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12">
         <v>0.36951250000000002</v>
@@ -2149,7 +2149,7 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16">
         <v>0.27938750000000001</v>
@@ -2205,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17">
         <v>0.27938750000000001</v>
@@ -2261,7 +2261,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <v>0.27938750000000001</v>
@@ -2317,7 +2317,7 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <v>0.27938750000000001</v>
@@ -2373,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>0.27938750000000001</v>
@@ -2429,7 +2429,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21">
         <v>0.27938750000000001</v>
@@ -2485,7 +2485,7 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22">
         <v>0.27938750000000001</v>
@@ -2541,7 +2541,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23">
         <v>0.27938750000000001</v>
@@ -2653,7 +2653,7 @@
         <v>178</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>0.35148750000000001</v>
@@ -2709,7 +2709,7 @@
         <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26">
         <v>0.27037500000000003</v>
@@ -2765,7 +2765,7 @@
         <v>178</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27">
         <v>0.27037500000000003</v>
@@ -2821,7 +2821,7 @@
         <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E28">
         <v>0.27037500000000003</v>
@@ -2877,7 +2877,7 @@
         <v>178</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29">
         <v>0.27037500000000003</v>
@@ -2933,7 +2933,7 @@
         <v>178</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30">
         <v>0.27037500000000003</v>
@@ -2989,7 +2989,7 @@
         <v>178</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31">
         <v>0.27037500000000003</v>
@@ -3045,7 +3045,7 @@
         <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E32">
         <v>0.27037500000000003</v>
@@ -3101,7 +3101,7 @@
         <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33">
         <v>0.27037500000000003</v>
@@ -3155,7 +3155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02320C4A-D1D4-4132-A48C-6BFDEAE214E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6944A3D-1D3A-48F6-A02B-D0E32821DD4A}">
   <dimension ref="B9:T246"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3343,19 +3343,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>9.4079266895761751E-2</v>
+        <v>1.6456357388316155E-2</v>
       </c>
       <c r="G13">
-        <v>0.59739999999999993</v>
+        <v>0.57680000000000009</v>
       </c>
       <c r="H13">
-        <v>1265</v>
+        <v>1485.0000000000002</v>
       </c>
       <c r="I13">
-        <v>36.300000000000004</v>
+        <v>42.900000000000006</v>
       </c>
       <c r="J13">
-        <v>3.4650000000000003</v>
+        <v>3.78</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -3396,19 +3396,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>1.6456357388316155E-2</v>
+        <v>9.4079266895761751E-2</v>
       </c>
       <c r="G14">
-        <v>0.57680000000000009</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H14">
-        <v>1485.0000000000002</v>
+        <v>1265</v>
       </c>
       <c r="I14">
-        <v>42.900000000000006</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J14">
-        <v>3.78</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -3496,7 +3496,7 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>1988</v>
@@ -3549,7 +3549,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17">
         <v>2023</v>
@@ -3602,7 +3602,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <v>2023</v>
@@ -3655,7 +3655,7 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <v>2023</v>
@@ -3708,7 +3708,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>2023</v>
@@ -3761,7 +3761,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21">
         <v>2023</v>
@@ -3814,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22">
         <v>2023</v>
@@ -3867,7 +3867,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23">
         <v>2023</v>
@@ -3920,7 +3920,7 @@
         <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>2023</v>
@@ -3979,19 +3979,19 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>1.9501591060460302E-2</v>
+        <v>5.8034855324502345E-2</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>3712.5</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I25">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J25">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4032,19 +4032,19 @@
         <v>2022</v>
       </c>
       <c r="F26">
-        <v>5.8034855324502345E-2</v>
+        <v>1.5272330348553248E-2</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I26">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J26">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4085,19 +4085,19 @@
         <v>2022</v>
       </c>
       <c r="F27">
-        <v>1.4332494634796125E-2</v>
+        <v>0.34844409087545336</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I27">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J27">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4138,13 +4138,13 @@
         <v>2022</v>
       </c>
       <c r="F28">
-        <v>4.2292607119070534E-2</v>
+        <v>1.6447124990749649E-2</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>3712.5000000000009</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I28">
         <v>71.5</v>
@@ -4191,19 +4191,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>2.1851180344853109E-2</v>
+        <v>8.7169762450973159E-2</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I29">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J29">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4244,19 +4244,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>2.6785317842078004E-2</v>
+        <v>0.12617294457189376</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I30">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J30">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -4297,7 +4297,7 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>2.8195071412713692E-2</v>
+        <v>2.6315399985199443E-2</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -4309,7 +4309,7 @@
         <v>71.5</v>
       </c>
       <c r="J31">
-        <v>2.5200000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4350,13 +4350,13 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>1.7152001776067495E-2</v>
+        <v>1.9501591060460302E-2</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>3712.5000000000005</v>
+        <v>3712.5</v>
       </c>
       <c r="I32">
         <v>71.5</v>
@@ -4403,19 +4403,19 @@
         <v>2022</v>
       </c>
       <c r="F33">
-        <v>0.34844409087545336</v>
+        <v>0.1047916820839192</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I33">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J33">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -4456,7 +4456,7 @@
         <v>2022</v>
       </c>
       <c r="F34">
-        <v>1.6447124990749649E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -4509,13 +4509,13 @@
         <v>2022</v>
       </c>
       <c r="F35">
-        <v>8.7169762450973159E-2</v>
+        <v>6.5788499962998598E-2</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>3162.5000000000009</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I35">
         <v>60.500000000000014</v>
@@ -4562,19 +4562,19 @@
         <v>2022</v>
       </c>
       <c r="F36">
-        <v>0.12617294457189376</v>
+        <v>3.1249537482424337E-2</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I36">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J36">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -4615,7 +4615,7 @@
         <v>2022</v>
       </c>
       <c r="F37">
-        <v>2.6315399985199443E-2</v>
+        <v>2.5140605343003043E-2</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4668,19 +4668,19 @@
         <v>2022</v>
       </c>
       <c r="F38">
-        <v>7.9886035669355454E-2</v>
+        <v>2.866498926959225E-2</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I38">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J38">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -4721,7 +4721,7 @@
         <v>2022</v>
       </c>
       <c r="F39">
-        <v>0.1047916820839192</v>
+        <v>6.0619403537334436E-2</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4774,7 +4774,7 @@
         <v>2022</v>
       </c>
       <c r="F40">
-        <v>1.268778213572116E-2</v>
+        <v>3.9943017834677727E-2</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4827,19 +4827,19 @@
         <v>2022</v>
       </c>
       <c r="F41">
-        <v>4.2292607119070534E-2</v>
+        <v>5.2160882113520331E-2</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>3712.5000000000009</v>
+        <v>3162.5000000000009</v>
       </c>
       <c r="I41">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J41">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K41">
         <v>100</v>
@@ -4880,19 +4880,19 @@
         <v>2022</v>
       </c>
       <c r="F42">
-        <v>4.3702360689706218E-2</v>
+        <v>7.8241323170280486E-2</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I42">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J42">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -4933,7 +4933,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>3.1719455339302899E-2</v>
+        <v>1.2217864278842598E-2</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4942,7 +4942,7 @@
         <v>3712.5000000000005</v>
       </c>
       <c r="I43">
-        <v>71.499999999999986</v>
+        <v>71.5</v>
       </c>
       <c r="J43">
         <v>2.52</v>
@@ -4986,13 +4986,13 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>5.2160882113520331E-2</v>
+        <v>0.21146303559535268</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44">
-        <v>3162.5000000000009</v>
+        <v>3162.5</v>
       </c>
       <c r="I44">
         <v>60.500000000000014</v>
@@ -5039,19 +5039,19 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>7.8241323170280486E-2</v>
+        <v>1.5037371420113967E-2</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I45">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J45">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K45">
         <v>100</v>
@@ -5092,19 +5092,19 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>1.2217864278842598E-2</v>
+        <v>0.11278028565085477</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I46">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J46">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K46">
         <v>100</v>
@@ -5145,19 +5145,19 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.21146303559535268</v>
+        <v>1.0573151779767634E-2</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47">
-        <v>3162.5</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I47">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J47">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K47">
         <v>100</v>
@@ -5192,13 +5192,13 @@
         <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>1.5037371420113967E-2</v>
+        <v>1.1747946421964037E-2</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -5245,25 +5245,25 @@
         <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E49">
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.11278028565085477</v>
+        <v>4.3702360689706218E-2</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I49">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J49">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K49">
         <v>100</v>
@@ -5298,25 +5298,25 @@
         <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>4.3702360689706218E-2</v>
+        <v>7.9886035669355454E-2</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I50">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J50">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K50">
         <v>100</v>
@@ -5351,13 +5351,13 @@
         <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>2.3495892843928074E-2</v>
+        <v>2.6785317842078004E-2</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5404,25 +5404,25 @@
         <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>2.866498926959225E-2</v>
+        <v>7.8006364241841208E-2</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I52">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J52">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K52">
         <v>100</v>
@@ -5457,25 +5457,25 @@
         <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53">
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>7.8006364241841208E-2</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I53">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J53">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K53">
         <v>100</v>
@@ -5510,13 +5510,13 @@
         <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54">
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>2.3495892843928074E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5563,19 +5563,19 @@
         <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>1.9031673203581741E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I55">
         <v>71.5</v>
@@ -5616,19 +5616,19 @@
         <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>1.1043069636646195E-2</v>
+        <v>1.7152001776067495E-2</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>3712.5</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I56">
         <v>71.5</v>
@@ -5669,13 +5669,13 @@
         <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>1.7386960704506776E-2</v>
+        <v>3.1719455339302899E-2</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -5684,7 +5684,7 @@
         <v>3712.5000000000005</v>
       </c>
       <c r="I57">
-        <v>71.5</v>
+        <v>71.499999999999986</v>
       </c>
       <c r="J57">
         <v>2.52</v>
@@ -5722,25 +5722,25 @@
         <v>31</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.38815214978169182</v>
+        <v>1.9031673203581741E-2</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I58">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J58">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K58">
         <v>100</v>
@@ -5775,13 +5775,13 @@
         <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>3.5243839265892113E-2</v>
+        <v>4.6521867830977587E-2</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -5828,13 +5828,13 @@
         <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>1.1747946421964037E-2</v>
+        <v>1.7386960704506776E-2</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -5881,25 +5881,25 @@
         <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>1.0573151779767634E-2</v>
+        <v>0.38815214978169182</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61">
-        <v>3712.5000000000009</v>
+        <v>2750</v>
       </c>
       <c r="I61">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J61">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K61">
         <v>100</v>
@@ -5934,13 +5934,13 @@
         <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>1.1747946421964037E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5993,7 +5993,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>5.9444608895138029E-2</v>
+        <v>7.0487678531784226E-2</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6002,7 +6002,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I63">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J63">
         <v>2.3100000000000005</v>
@@ -6046,7 +6046,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>2.7960112484274408E-2</v>
+        <v>2.3495892843928074E-2</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         <v>71.5</v>
       </c>
       <c r="J64">
-        <v>2.5199999999999996</v>
+        <v>2.52</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -6099,7 +6099,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>2.4200769629245916E-2</v>
+        <v>1.268778213572116E-2</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6152,13 +6152,13 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>4.2292607119070534E-2</v>
+        <v>1.1043069636646195E-2</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>3712.5000000000009</v>
+        <v>3712.5</v>
       </c>
       <c r="I66">
         <v>71.5</v>
@@ -6205,19 +6205,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.10925590172426554</v>
+        <v>3.5243839265892113E-2</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I67">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J67">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -6311,19 +6311,19 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>7.0487678531784226E-2</v>
+        <v>2.1851180344853109E-2</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I69">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J69">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -6364,19 +6364,19 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>1.268778213572116E-2</v>
+        <v>5.1690964256641762E-2</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I70">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J70">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -6417,7 +6417,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>2.0911344631095986E-2</v>
+        <v>2.3965810700806636E-2</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6470,19 +6470,19 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>1.5272330348553248E-2</v>
+        <v>0.10925590172426554</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I72">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J72">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -6523,19 +6523,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>9.1164064234440928E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I73">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J73">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -6576,19 +6576,19 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>5.1690964256641762E-2</v>
+        <v>2.4200769629245916E-2</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I74">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J74">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -6629,7 +6629,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>2.3965810700806636E-2</v>
+        <v>2.7960112484274408E-2</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -6641,7 +6641,7 @@
         <v>71.5</v>
       </c>
       <c r="J75">
-        <v>2.52</v>
+        <v>2.5199999999999996</v>
       </c>
       <c r="K75">
         <v>100</v>
@@ -6682,19 +6682,19 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>6.5788499962998598E-2</v>
+        <v>1.4332494634796125E-2</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I76">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J76">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -6735,19 +6735,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>3.9943017834677727E-2</v>
+        <v>5.9444608895138029E-2</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I77">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J77">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -6788,19 +6788,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>6.0619403537334436E-2</v>
+        <v>2.0911344631095986E-2</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I78">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J78">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K78">
         <v>100</v>
@@ -6841,7 +6841,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>4.6521867830977587E-2</v>
+        <v>4.3702360689706218E-2</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -6894,19 +6894,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>2.5140605343003043E-2</v>
+        <v>9.1164064234440928E-2</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I80">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J80">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -6947,13 +6947,13 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>3.1249537482424337E-2</v>
+        <v>4.2292607119070534E-2</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
       <c r="H81">
-        <v>3712.5000000000005</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="I81">
         <v>71.5</v>
@@ -7000,7 +7000,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>1.268778213572116E-2</v>
+        <v>2.8195071412713692E-2</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -7012,7 +7012,7 @@
         <v>71.5</v>
       </c>
       <c r="J82">
-        <v>2.52</v>
+        <v>2.5200000000000005</v>
       </c>
       <c r="K82">
         <v>100</v>
@@ -7047,7 +7047,7 @@
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="E83">
         <v>1923</v>
@@ -7100,7 +7100,7 @@
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E84">
         <v>1962</v>
@@ -7153,7 +7153,7 @@
         <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E85">
         <v>1966</v>
@@ -7206,7 +7206,7 @@
         <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E86">
         <v>1959</v>
@@ -7259,7 +7259,7 @@
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E87">
         <v>1999</v>
@@ -7312,7 +7312,7 @@
         <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E88">
         <v>1955</v>
@@ -7365,7 +7365,7 @@
         <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E89">
         <v>1969</v>
@@ -7418,7 +7418,7 @@
         <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E90">
         <v>1959</v>
@@ -7471,7 +7471,7 @@
         <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E91">
         <v>1955</v>
@@ -7524,7 +7524,7 @@
         <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E92">
         <v>1957</v>
@@ -7577,7 +7577,7 @@
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E93">
         <v>1958</v>
@@ -7630,7 +7630,7 @@
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="E94">
         <v>1965</v>
@@ -7683,7 +7683,7 @@
         <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E95">
         <v>1962</v>
@@ -7736,7 +7736,7 @@
         <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E96">
         <v>1981</v>
@@ -7789,7 +7789,7 @@
         <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E97">
         <v>1928</v>
@@ -7842,7 +7842,7 @@
         <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E98">
         <v>2012</v>
@@ -7895,7 +7895,7 @@
         <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E99">
         <v>1950</v>
@@ -7948,7 +7948,7 @@
         <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E100">
         <v>1967</v>
@@ -8001,7 +8001,7 @@
         <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E101">
         <v>2016</v>
@@ -8054,7 +8054,7 @@
         <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E102">
         <v>1943</v>
@@ -8107,7 +8107,7 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="E103">
         <v>1978</v>
@@ -8160,7 +8160,7 @@
         <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E104">
         <v>1976</v>
@@ -8213,7 +8213,7 @@
         <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E105">
         <v>1910</v>
@@ -8266,7 +8266,7 @@
         <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E106">
         <v>1960</v>
@@ -8319,7 +8319,7 @@
         <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E107">
         <v>1966</v>
@@ -8372,7 +8372,7 @@
         <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E108">
         <v>1962</v>
@@ -8425,7 +8425,7 @@
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E109">
         <v>1970</v>
@@ -8478,7 +8478,7 @@
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="E110">
         <v>1956</v>
@@ -8531,7 +8531,7 @@
         <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E111">
         <v>1958</v>
@@ -8584,7 +8584,7 @@
         <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E112">
         <v>1957</v>
@@ -8637,7 +8637,7 @@
         <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E113">
         <v>1978</v>
@@ -8690,7 +8690,7 @@
         <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E114">
         <v>1968</v>
@@ -8743,7 +8743,7 @@
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E115">
         <v>1961</v>
@@ -8796,7 +8796,7 @@
         <v>31</v>
       </c>
       <c r="D116" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E116">
         <v>2015</v>
@@ -8849,7 +8849,7 @@
         <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E117">
         <v>1965</v>
@@ -8902,7 +8902,7 @@
         <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E118">
         <v>1962</v>
@@ -8955,7 +8955,7 @@
         <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E119">
         <v>1964</v>
@@ -9008,7 +9008,7 @@
         <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E120">
         <v>1953</v>
@@ -9061,7 +9061,7 @@
         <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E121">
         <v>1943</v>
@@ -9114,7 +9114,7 @@
         <v>31</v>
       </c>
       <c r="D122" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="E122">
         <v>1928</v>
@@ -9167,7 +9167,7 @@
         <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E123">
         <v>1947</v>
@@ -9220,7 +9220,7 @@
         <v>31</v>
       </c>
       <c r="D124" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E124">
         <v>1907</v>
@@ -9273,7 +9273,7 @@
         <v>31</v>
       </c>
       <c r="D125" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="E125">
         <v>1957</v>
@@ -9326,7 +9326,7 @@
         <v>31</v>
       </c>
       <c r="D126" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E126">
         <v>1992</v>
@@ -9379,7 +9379,7 @@
         <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E127">
         <v>1967</v>
@@ -9432,7 +9432,7 @@
         <v>31</v>
       </c>
       <c r="D128" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E128">
         <v>1926</v>
@@ -9485,7 +9485,7 @@
         <v>31</v>
       </c>
       <c r="D129" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E129">
         <v>1954</v>
@@ -9538,7 +9538,7 @@
         <v>31</v>
       </c>
       <c r="D130" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E130">
         <v>1921</v>
@@ -9591,7 +9591,7 @@
         <v>31</v>
       </c>
       <c r="D131" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="E131">
         <v>1958</v>
@@ -9644,7 +9644,7 @@
         <v>31</v>
       </c>
       <c r="D132" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="E132">
         <v>2014</v>
@@ -9697,7 +9697,7 @@
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E133">
         <v>1937</v>
@@ -9750,7 +9750,7 @@
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E134">
         <v>1962</v>
@@ -9803,7 +9803,7 @@
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E135">
         <v>1923</v>
@@ -9856,7 +9856,7 @@
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E136">
         <v>2016</v>
@@ -9909,7 +9909,7 @@
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="E137">
         <v>1977</v>
@@ -9962,7 +9962,7 @@
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E138">
         <v>2022</v>
@@ -10015,7 +10015,7 @@
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E139">
         <v>2009</v>
@@ -10068,7 +10068,7 @@
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E140">
         <v>2026</v>
@@ -10121,7 +10121,7 @@
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E141">
         <v>1968</v>
@@ -10174,7 +10174,7 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E142">
         <v>1972</v>
@@ -10227,7 +10227,7 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E143">
         <v>2017</v>
@@ -10280,7 +10280,7 @@
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E144">
         <v>1958</v>
@@ -10333,7 +10333,7 @@
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E145">
         <v>1976</v>
@@ -10386,7 +10386,7 @@
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E146">
         <v>1955</v>
@@ -10439,7 +10439,7 @@
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E147">
         <v>1926</v>
@@ -10492,7 +10492,7 @@
         <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E148">
         <v>1966</v>
@@ -10545,7 +10545,7 @@
         <v>31</v>
       </c>
       <c r="D149" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="E149">
         <v>1950</v>
@@ -10598,7 +10598,7 @@
         <v>31</v>
       </c>
       <c r="D150" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E150">
         <v>1959</v>
@@ -10651,7 +10651,7 @@
         <v>31</v>
       </c>
       <c r="D151" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E151">
         <v>1908</v>
@@ -10704,7 +10704,7 @@
         <v>31</v>
       </c>
       <c r="D152" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E152">
         <v>1960</v>
@@ -10757,7 +10757,7 @@
         <v>31</v>
       </c>
       <c r="D153" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E153">
         <v>1925</v>
@@ -10810,7 +10810,7 @@
         <v>31</v>
       </c>
       <c r="D154" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E154">
         <v>1920</v>
@@ -10863,7 +10863,7 @@
         <v>31</v>
       </c>
       <c r="D155" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E155">
         <v>1975</v>
@@ -10916,7 +10916,7 @@
         <v>31</v>
       </c>
       <c r="D156" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E156">
         <v>1967</v>
@@ -10969,7 +10969,7 @@
         <v>31</v>
       </c>
       <c r="D157" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="E157">
         <v>1952</v>
@@ -11022,7 +11022,7 @@
         <v>31</v>
       </c>
       <c r="D158" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E158">
         <v>1932</v>
@@ -11075,7 +11075,7 @@
         <v>31</v>
       </c>
       <c r="D159" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E159">
         <v>1958</v>
@@ -11128,7 +11128,7 @@
         <v>31</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E160">
         <v>1920</v>
@@ -11181,7 +11181,7 @@
         <v>31</v>
       </c>
       <c r="D161" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E161">
         <v>1947</v>
@@ -11234,7 +11234,7 @@
         <v>31</v>
       </c>
       <c r="D162" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E162">
         <v>1952</v>
@@ -11552,7 +11552,7 @@
         <v>178</v>
       </c>
       <c r="D168" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E168">
         <v>1988</v>
@@ -11605,7 +11605,7 @@
         <v>178</v>
       </c>
       <c r="D169" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E169">
         <v>2023</v>
@@ -11658,7 +11658,7 @@
         <v>178</v>
       </c>
       <c r="D170" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E170">
         <v>2023</v>
@@ -11711,7 +11711,7 @@
         <v>178</v>
       </c>
       <c r="D171" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E171">
         <v>2023</v>
@@ -11764,7 +11764,7 @@
         <v>178</v>
       </c>
       <c r="D172" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E172">
         <v>2023</v>
@@ -11817,7 +11817,7 @@
         <v>178</v>
       </c>
       <c r="D173" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E173">
         <v>2023</v>
@@ -11870,7 +11870,7 @@
         <v>178</v>
       </c>
       <c r="D174" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E174">
         <v>2023</v>
@@ -11923,7 +11923,7 @@
         <v>178</v>
       </c>
       <c r="D175" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E175">
         <v>2023</v>
@@ -11976,7 +11976,7 @@
         <v>178</v>
       </c>
       <c r="D176" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E176">
         <v>2023</v>
@@ -12053,7 +12053,7 @@
         <v>33</v>
       </c>
       <c r="L177">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N177" t="s">
         <v>259</v>
@@ -12165,7 +12165,7 @@
         <v>33</v>
       </c>
       <c r="L179">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N179" t="s">
         <v>259</v>
@@ -12333,7 +12333,7 @@
         <v>33</v>
       </c>
       <c r="L182">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N182" t="s">
         <v>259</v>
@@ -12389,7 +12389,7 @@
         <v>33</v>
       </c>
       <c r="L183">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N183" t="s">
         <v>259</v>
@@ -12669,7 +12669,7 @@
         <v>33</v>
       </c>
       <c r="L188">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N188" t="s">
         <v>259</v>
@@ -12949,7 +12949,7 @@
         <v>33</v>
       </c>
       <c r="L193">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N193" t="s">
         <v>259</v>
@@ -13061,7 +13061,7 @@
         <v>33</v>
       </c>
       <c r="L195">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N195" t="s">
         <v>259</v>
@@ -13229,7 +13229,7 @@
         <v>33</v>
       </c>
       <c r="L198">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N198" t="s">
         <v>259</v>
@@ -13341,7 +13341,7 @@
         <v>33</v>
       </c>
       <c r="L200">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N200" t="s">
         <v>259</v>
@@ -13397,7 +13397,7 @@
         <v>33</v>
       </c>
       <c r="L201">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N201" t="s">
         <v>259</v>
@@ -13621,7 +13621,7 @@
         <v>33</v>
       </c>
       <c r="L205">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
       <c r="N205" t="s">
         <v>259</v>
@@ -13845,7 +13845,7 @@
         <v>33</v>
       </c>
       <c r="L209">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="210" spans="2:12" x14ac:dyDescent="0.45">
@@ -13880,7 +13880,7 @@
         <v>33</v>
       </c>
       <c r="L210">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="211" spans="2:12" x14ac:dyDescent="0.45">
@@ -13915,7 +13915,7 @@
         <v>33</v>
       </c>
       <c r="L211">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="212" spans="2:12" x14ac:dyDescent="0.45">
@@ -14090,7 +14090,7 @@
         <v>33</v>
       </c>
       <c r="L216">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.45">
@@ -14265,7 +14265,7 @@
         <v>33</v>
       </c>
       <c r="L221">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="222" spans="2:12" x14ac:dyDescent="0.45">
@@ -14335,7 +14335,7 @@
         <v>33</v>
       </c>
       <c r="L223">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="224" spans="2:12" x14ac:dyDescent="0.45">
@@ -14370,7 +14370,7 @@
         <v>33</v>
       </c>
       <c r="L224">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="225" spans="2:12" x14ac:dyDescent="0.45">
@@ -14580,7 +14580,7 @@
         <v>33</v>
       </c>
       <c r="L230">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="231" spans="2:12" x14ac:dyDescent="0.45">
@@ -14615,7 +14615,7 @@
         <v>33</v>
       </c>
       <c r="L231">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="232" spans="2:12" x14ac:dyDescent="0.45">
@@ -14650,7 +14650,7 @@
         <v>33</v>
       </c>
       <c r="L232">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="233" spans="2:12" x14ac:dyDescent="0.45">
@@ -14755,7 +14755,7 @@
         <v>33</v>
       </c>
       <c r="L235">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="236" spans="2:12" x14ac:dyDescent="0.45">
@@ -14825,7 +14825,7 @@
         <v>33</v>
       </c>
       <c r="L237">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="238" spans="2:12" x14ac:dyDescent="0.45">
@@ -14860,7 +14860,7 @@
         <v>33</v>
       </c>
       <c r="L238">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="239" spans="2:12" x14ac:dyDescent="0.45">
@@ -14895,7 +14895,7 @@
         <v>33</v>
       </c>
       <c r="L239">
-        <v>0.16885857771052634</v>
+        <v>0.16885857771052631</v>
       </c>
     </row>
     <row r="240" spans="2:12" x14ac:dyDescent="0.45">
@@ -15044,7 +15044,7 @@
         <v>241</v>
       </c>
       <c r="D246" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E246">
         <v>2022</v>
